--- a/public/templates/SALES_AMAZON_TEMPLATE.xlsx
+++ b/public/templates/SALES_AMAZON_TEMPLATE.xlsx
@@ -107,22 +107,22 @@
     <t>Colour</t>
   </si>
   <si>
-    <t>AMAZON-EXAMPLE</t>
+    <t>AMZ-5001</t>
   </si>
   <si>
-    <t>SG-A24-128-DS-BK-EX</t>
+    <t>IP13-128-MID</t>
   </si>
   <si>
-    <t>350100000000001</t>
+    <t>350100000000000</t>
   </si>
   <si>
-    <t>EXAMPLE SUPPLIER</t>
+    <t>MOBILE WHOLESALE LTD</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Samsung Galaxy A24 128GB</t>
+    <t>Apple iPhone 13 128GB</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -785,10 +785,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="H2" s="3">
-        <v>139.99</v>
+        <v>425</v>
       </c>
       <c r="I2" s="3">
         <f>IF($H2="","",H2-G2)</f>
@@ -809,7 +809,7 @@
         <f>IF($H2="","",M2*20%)</f>
       </c>
       <c r="O2" s="3">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="P2" s="3">
         <f>IF($H2="","",O2*20%)</f>

--- a/public/templates/SALES_AMAZON_TEMPLATE.xlsx
+++ b/public/templates/SALES_AMAZON_TEMPLATE.xlsx
@@ -791,43 +791,43 @@
         <v>425</v>
       </c>
       <c r="I2" s="3">
-        <f>IF($H2="","",H2-G2)</f>
+        <f>H2-G2</f>
       </c>
       <c r="J2" s="3">
-        <f>IF($H2="","",I2*16.67%)</f>
+        <f>I2*16.67%</f>
       </c>
       <c r="K2" s="3">
-        <f>IF($H2="","",H2/100*7)</f>
+        <f>H2/100*7</f>
       </c>
       <c r="L2" s="3">
-        <f>IF($H2="","",K2*20%)</f>
+        <f>K2*20%</f>
       </c>
       <c r="M2" s="3">
-        <f>IF($H2="","",K2*2%)</f>
+        <f>K2*2%</f>
       </c>
       <c r="N2" s="3">
-        <f>IF($H2="","",M2*20%)</f>
+        <f>M2*20%</f>
       </c>
       <c r="O2" s="3">
         <v>8</v>
       </c>
       <c r="P2" s="3">
-        <f>IF($H2="","",O2*20%)</f>
+        <f>O2*20%</f>
       </c>
       <c r="Q2" s="3">
         <v>1</v>
       </c>
       <c r="R2" s="3">
-        <f>IF($H2="","",L2+N2+P2)</f>
+        <f>L2+N2+P2</f>
       </c>
       <c r="S2" s="3">
-        <f>IF($H2="","",I2-J2-K2-L2-M2-N2-O2-P2-Q2)</f>
+        <f>I2-J2-K2-L2-M2-N2-O2-P2-Q2</f>
       </c>
       <c r="T2" s="3">
-        <f>IF($H2="","",(S2-AB2)/G2*100)</f>
+        <f>(S2-AB2)/G2*100</f>
       </c>
       <c r="U2" s="3">
-        <f>IF($H2="","",J2-R2)</f>
+        <f>J2-R2</f>
       </c>
       <c r="V2" t="s">
         <v>35</v>
@@ -836,7 +836,7 @@
         <v>36</v>
       </c>
       <c r="AC2" s="3">
-        <f>IF($H2="","",S2-AB2)</f>
+        <f>S2-AB2</f>
       </c>
       <c r="AD2" t="s">
         <v>35</v>
@@ -845,7 +845,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="G3" s="3"/>
@@ -891,7 +891,7 @@
         <f>IF($H3="","",S3-AB3)</f>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="G4" s="3"/>
@@ -937,7 +937,7 @@
         <f>IF($H4="","",S4-AB4)</f>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="G5" s="3"/>
@@ -983,7 +983,7 @@
         <f>IF($H5="","",S5-AB5)</f>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="G6" s="3"/>
@@ -1029,7 +1029,7 @@
         <f>IF($H6="","",S6-AB6)</f>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="G7" s="3"/>
@@ -1075,7 +1075,7 @@
         <f>IF($H7="","",S7-AB7)</f>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="G8" s="3"/>
@@ -1121,7 +1121,7 @@
         <f>IF($H8="","",S8-AB8)</f>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="G9" s="3"/>
@@ -1167,7 +1167,7 @@
         <f>IF($H9="","",S9-AB9)</f>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="G10" s="3"/>
@@ -1213,7 +1213,7 @@
         <f>IF($H10="","",S10-AB10)</f>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="G11" s="3"/>
@@ -1259,7 +1259,7 @@
         <f>IF($H11="","",S11-AB11)</f>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="G12" s="3"/>
@@ -1305,7 +1305,7 @@
         <f>IF($H12="","",S12-AB12)</f>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="G13" s="3"/>
@@ -1351,7 +1351,7 @@
         <f>IF($H13="","",S13-AB13)</f>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="G14" s="3"/>
@@ -1397,7 +1397,7 @@
         <f>IF($H14="","",S14-AB14)</f>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="G15" s="3"/>
@@ -1443,7 +1443,7 @@
         <f>IF($H15="","",S15-AB15)</f>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="G16" s="3"/>
@@ -1489,7 +1489,7 @@
         <f>IF($H16="","",S16-AB16)</f>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="G17" s="3"/>
@@ -1535,7 +1535,7 @@
         <f>IF($H17="","",S17-AB17)</f>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="G18" s="3"/>
@@ -1581,7 +1581,7 @@
         <f>IF($H18="","",S18-AB18)</f>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="G19" s="3"/>
@@ -1627,7 +1627,7 @@
         <f>IF($H19="","",S19-AB19)</f>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="G20" s="3"/>
@@ -1673,7 +1673,7 @@
         <f>IF($H20="","",S20-AB20)</f>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="G21" s="3"/>
@@ -1719,7 +1719,7 @@
         <f>IF($H21="","",S21-AB21)</f>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="G22" s="3"/>
@@ -1765,7 +1765,7 @@
         <f>IF($H22="","",S22-AB22)</f>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="G23" s="3"/>
@@ -1811,7 +1811,7 @@
         <f>IF($H23="","",S23-AB23)</f>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="G24" s="3"/>
@@ -1857,7 +1857,7 @@
         <f>IF($H24="","",S24-AB24)</f>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="G25" s="3"/>
@@ -1903,7 +1903,7 @@
         <f>IF($H25="","",S25-AB25)</f>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="G26" s="3"/>
@@ -1949,7 +1949,7 @@
         <f>IF($H26="","",S26-AB26)</f>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="G27" s="3"/>
@@ -1995,7 +1995,7 @@
         <f>IF($H27="","",S27-AB27)</f>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="G28" s="3"/>
@@ -2041,7 +2041,7 @@
         <f>IF($H28="","",S28-AB28)</f>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="G29" s="3"/>
@@ -2087,7 +2087,7 @@
         <f>IF($H29="","",S29-AB29)</f>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="G30" s="3"/>
@@ -2133,7 +2133,7 @@
         <f>IF($H30="","",S30-AB30)</f>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="G31" s="3"/>
@@ -2179,7 +2179,7 @@
         <f>IF($H31="","",S31-AB31)</f>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="G32" s="3"/>
@@ -2225,7 +2225,7 @@
         <f>IF($H32="","",S32-AB32)</f>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="G33" s="3"/>
@@ -2271,7 +2271,7 @@
         <f>IF($H33="","",S33-AB33)</f>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="G34" s="3"/>
@@ -2317,7 +2317,7 @@
         <f>IF($H34="","",S34-AB34)</f>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="G35" s="3"/>
@@ -2363,7 +2363,7 @@
         <f>IF($H35="","",S35-AB35)</f>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="G36" s="3"/>
@@ -2409,7 +2409,7 @@
         <f>IF($H36="","",S36-AB36)</f>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="G37" s="3"/>
@@ -2455,7 +2455,7 @@
         <f>IF($H37="","",S37-AB37)</f>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="G38" s="3"/>
@@ -2501,7 +2501,7 @@
         <f>IF($H38="","",S38-AB38)</f>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="G39" s="3"/>
@@ -2547,7 +2547,7 @@
         <f>IF($H39="","",S39-AB39)</f>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="G40" s="3"/>
@@ -2593,7 +2593,7 @@
         <f>IF($H40="","",S40-AB40)</f>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="G41" s="3"/>
@@ -2639,7 +2639,7 @@
         <f>IF($H41="","",S41-AB41)</f>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="G42" s="3"/>
@@ -2685,7 +2685,7 @@
         <f>IF($H42="","",S42-AB42)</f>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="G43" s="3"/>
@@ -2731,7 +2731,7 @@
         <f>IF($H43="","",S43-AB43)</f>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="G44" s="3"/>
@@ -2777,7 +2777,7 @@
         <f>IF($H44="","",S44-AB44)</f>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="G45" s="3"/>
@@ -2823,7 +2823,7 @@
         <f>IF($H45="","",S45-AB45)</f>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="G46" s="3"/>
@@ -2869,7 +2869,7 @@
         <f>IF($H46="","",S46-AB46)</f>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="G47" s="3"/>
@@ -2915,7 +2915,7 @@
         <f>IF($H47="","",S47-AB47)</f>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="G48" s="3"/>
@@ -2961,7 +2961,7 @@
         <f>IF($H48="","",S48-AB48)</f>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="G49" s="3"/>
@@ -3007,7 +3007,7 @@
         <f>IF($H49="","",S49-AB49)</f>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="G50" s="3"/>
@@ -3053,7 +3053,7 @@
         <f>IF($H50="","",S50-AB50)</f>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="G51" s="3"/>
@@ -3099,7 +3099,7 @@
         <f>IF($H51="","",S51-AB51)</f>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="G52" s="3"/>
@@ -3145,7 +3145,7 @@
         <f>IF($H52="","",S52-AB52)</f>
       </c>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="G53" s="3"/>
@@ -3191,7 +3191,7 @@
         <f>IF($H53="","",S53-AB53)</f>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="G54" s="3"/>
@@ -3237,7 +3237,7 @@
         <f>IF($H54="","",S54-AB54)</f>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="G55" s="3"/>
@@ -3283,7 +3283,7 @@
         <f>IF($H55="","",S55-AB55)</f>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="G56" s="3"/>
@@ -3329,7 +3329,7 @@
         <f>IF($H56="","",S56-AB56)</f>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="G57" s="3"/>
@@ -3375,7 +3375,7 @@
         <f>IF($H57="","",S57-AB57)</f>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="G58" s="3"/>
@@ -3421,7 +3421,7 @@
         <f>IF($H58="","",S58-AB58)</f>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="G59" s="3"/>
@@ -3467,7 +3467,7 @@
         <f>IF($H59="","",S59-AB59)</f>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="G60" s="3"/>
@@ -3513,7 +3513,7 @@
         <f>IF($H60="","",S60-AB60)</f>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="G61" s="3"/>
@@ -3559,7 +3559,7 @@
         <f>IF($H61="","",S61-AB61)</f>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="G62" s="3"/>
@@ -3605,7 +3605,7 @@
         <f>IF($H62="","",S62-AB62)</f>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="G63" s="3"/>
@@ -3651,7 +3651,7 @@
         <f>IF($H63="","",S63-AB63)</f>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="G64" s="3"/>
@@ -3697,7 +3697,7 @@
         <f>IF($H64="","",S64-AB64)</f>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="G65" s="3"/>
@@ -3743,7 +3743,7 @@
         <f>IF($H65="","",S65-AB65)</f>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="G66" s="3"/>
@@ -3789,7 +3789,7 @@
         <f>IF($H66="","",S66-AB66)</f>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="G67" s="3"/>
@@ -3835,7 +3835,7 @@
         <f>IF($H67="","",S67-AB67)</f>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="G68" s="3"/>
@@ -3881,7 +3881,7 @@
         <f>IF($H68="","",S68-AB68)</f>
       </c>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="G69" s="3"/>
@@ -3927,7 +3927,7 @@
         <f>IF($H69="","",S69-AB69)</f>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="G70" s="3"/>
@@ -3973,7 +3973,7 @@
         <f>IF($H70="","",S70-AB70)</f>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="G71" s="3"/>
@@ -4019,7 +4019,7 @@
         <f>IF($H71="","",S71-AB71)</f>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="G72" s="3"/>
@@ -4065,7 +4065,7 @@
         <f>IF($H72="","",S72-AB72)</f>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="G73" s="3"/>
@@ -4111,7 +4111,7 @@
         <f>IF($H73="","",S73-AB73)</f>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="G74" s="3"/>
@@ -4157,7 +4157,7 @@
         <f>IF($H74="","",S74-AB74)</f>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="G75" s="3"/>
@@ -4203,7 +4203,7 @@
         <f>IF($H75="","",S75-AB75)</f>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="G76" s="3"/>
@@ -4249,7 +4249,7 @@
         <f>IF($H76="","",S76-AB76)</f>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="G77" s="3"/>
@@ -4295,7 +4295,7 @@
         <f>IF($H77="","",S77-AB77)</f>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="G78" s="3"/>
@@ -4341,7 +4341,7 @@
         <f>IF($H78="","",S78-AB78)</f>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="G79" s="3"/>
@@ -4387,7 +4387,7 @@
         <f>IF($H79="","",S79-AB79)</f>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="G80" s="3"/>
@@ -4433,7 +4433,7 @@
         <f>IF($H80="","",S80-AB80)</f>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="G81" s="3"/>
@@ -4479,7 +4479,7 @@
         <f>IF($H81="","",S81-AB81)</f>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="G82" s="3"/>
@@ -4525,7 +4525,7 @@
         <f>IF($H82="","",S82-AB82)</f>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="G83" s="3"/>
@@ -4571,7 +4571,7 @@
         <f>IF($H83="","",S83-AB83)</f>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="G84" s="3"/>
@@ -4617,7 +4617,7 @@
         <f>IF($H84="","",S84-AB84)</f>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="G85" s="3"/>
@@ -4663,7 +4663,7 @@
         <f>IF($H85="","",S85-AB85)</f>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="G86" s="3"/>
@@ -4709,7 +4709,7 @@
         <f>IF($H86="","",S86-AB86)</f>
       </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="G87" s="3"/>
@@ -4755,7 +4755,7 @@
         <f>IF($H87="","",S87-AB87)</f>
       </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="G88" s="3"/>
@@ -4801,7 +4801,7 @@
         <f>IF($H88="","",S88-AB88)</f>
       </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="G89" s="3"/>
@@ -4847,7 +4847,7 @@
         <f>IF($H89="","",S89-AB89)</f>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="G90" s="3"/>
@@ -4893,7 +4893,7 @@
         <f>IF($H90="","",S90-AB90)</f>
       </c>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="G91" s="3"/>
@@ -4939,7 +4939,7 @@
         <f>IF($H91="","",S91-AB91)</f>
       </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="G92" s="3"/>
@@ -4985,7 +4985,7 @@
         <f>IF($H92="","",S92-AB92)</f>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="G93" s="3"/>
@@ -5031,7 +5031,7 @@
         <f>IF($H93="","",S93-AB93)</f>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="G94" s="3"/>
@@ -5077,7 +5077,7 @@
         <f>IF($H94="","",S94-AB94)</f>
       </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="G95" s="3"/>
@@ -5123,7 +5123,7 @@
         <f>IF($H95="","",S95-AB95)</f>
       </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="G96" s="3"/>
@@ -5169,7 +5169,7 @@
         <f>IF($H96="","",S96-AB96)</f>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="G97" s="3"/>
@@ -5215,7 +5215,7 @@
         <f>IF($H97="","",S97-AB97)</f>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="G98" s="3"/>
@@ -5261,7 +5261,7 @@
         <f>IF($H98="","",S98-AB98)</f>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="G99" s="3"/>
@@ -5307,7 +5307,7 @@
         <f>IF($H99="","",S99-AB99)</f>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="G100" s="3"/>
@@ -5353,7 +5353,7 @@
         <f>IF($H100="","",S100-AB100)</f>
       </c>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="G101" s="3"/>
@@ -5399,7 +5399,7 @@
         <f>IF($H101="","",S101-AB101)</f>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="G102" s="3"/>
@@ -5445,7 +5445,7 @@
         <f>IF($H102="","",S102-AB102)</f>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="G103" s="3"/>
@@ -5491,7 +5491,7 @@
         <f>IF($H103="","",S103-AB103)</f>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="G104" s="3"/>
@@ -5537,7 +5537,7 @@
         <f>IF($H104="","",S104-AB104)</f>
       </c>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="G105" s="3"/>
@@ -5583,7 +5583,7 @@
         <f>IF($H105="","",S105-AB105)</f>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="G106" s="3"/>
@@ -5629,7 +5629,7 @@
         <f>IF($H106="","",S106-AB106)</f>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="G107" s="3"/>
@@ -5675,7 +5675,7 @@
         <f>IF($H107="","",S107-AB107)</f>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="G108" s="3"/>
@@ -5721,7 +5721,7 @@
         <f>IF($H108="","",S108-AB108)</f>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="G109" s="3"/>
@@ -5767,7 +5767,7 @@
         <f>IF($H109="","",S109-AB109)</f>
       </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="G110" s="3"/>
@@ -5813,7 +5813,7 @@
         <f>IF($H110="","",S110-AB110)</f>
       </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="G111" s="3"/>
@@ -5859,7 +5859,7 @@
         <f>IF($H111="","",S111-AB111)</f>
       </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="G112" s="3"/>
@@ -5905,7 +5905,7 @@
         <f>IF($H112="","",S112-AB112)</f>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="G113" s="3"/>
@@ -5951,7 +5951,7 @@
         <f>IF($H113="","",S113-AB113)</f>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="G114" s="3"/>
@@ -5997,7 +5997,7 @@
         <f>IF($H114="","",S114-AB114)</f>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="G115" s="3"/>
@@ -6043,7 +6043,7 @@
         <f>IF($H115="","",S115-AB115)</f>
       </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="G116" s="3"/>
@@ -6089,7 +6089,7 @@
         <f>IF($H116="","",S116-AB116)</f>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="G117" s="3"/>
@@ -6135,7 +6135,7 @@
         <f>IF($H117="","",S117-AB117)</f>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="G118" s="3"/>
@@ -6181,7 +6181,7 @@
         <f>IF($H118="","",S118-AB118)</f>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="G119" s="3"/>
@@ -6227,7 +6227,7 @@
         <f>IF($H119="","",S119-AB119)</f>
       </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="G120" s="3"/>
@@ -6273,7 +6273,7 @@
         <f>IF($H120="","",S120-AB120)</f>
       </c>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="G121" s="3"/>
@@ -6319,7 +6319,7 @@
         <f>IF($H121="","",S121-AB121)</f>
       </c>
     </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="G122" s="3"/>
@@ -6365,7 +6365,7 @@
         <f>IF($H122="","",S122-AB122)</f>
       </c>
     </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="G123" s="3"/>
@@ -6411,7 +6411,7 @@
         <f>IF($H123="","",S123-AB123)</f>
       </c>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="G124" s="3"/>
@@ -6457,7 +6457,7 @@
         <f>IF($H124="","",S124-AB124)</f>
       </c>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="G125" s="3"/>
@@ -6503,7 +6503,7 @@
         <f>IF($H125="","",S125-AB125)</f>
       </c>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="G126" s="3"/>
@@ -6549,7 +6549,7 @@
         <f>IF($H126="","",S126-AB126)</f>
       </c>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="G127" s="3"/>
@@ -6595,7 +6595,7 @@
         <f>IF($H127="","",S127-AB127)</f>
       </c>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="G128" s="3"/>
@@ -6641,7 +6641,7 @@
         <f>IF($H128="","",S128-AB128)</f>
       </c>
     </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="G129" s="3"/>
@@ -6687,7 +6687,7 @@
         <f>IF($H129="","",S129-AB129)</f>
       </c>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="G130" s="3"/>
@@ -6733,7 +6733,7 @@
         <f>IF($H130="","",S130-AB130)</f>
       </c>
     </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="G131" s="3"/>
@@ -6779,7 +6779,7 @@
         <f>IF($H131="","",S131-AB131)</f>
       </c>
     </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="G132" s="3"/>
@@ -6825,7 +6825,7 @@
         <f>IF($H132="","",S132-AB132)</f>
       </c>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="G133" s="3"/>
@@ -6871,7 +6871,7 @@
         <f>IF($H133="","",S133-AB133)</f>
       </c>
     </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="G134" s="3"/>
@@ -6917,7 +6917,7 @@
         <f>IF($H134="","",S134-AB134)</f>
       </c>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="G135" s="3"/>
@@ -6963,7 +6963,7 @@
         <f>IF($H135="","",S135-AB135)</f>
       </c>
     </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="G136" s="3"/>
@@ -7009,7 +7009,7 @@
         <f>IF($H136="","",S136-AB136)</f>
       </c>
     </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="G137" s="3"/>
@@ -7055,7 +7055,7 @@
         <f>IF($H137="","",S137-AB137)</f>
       </c>
     </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="G138" s="3"/>
@@ -7101,7 +7101,7 @@
         <f>IF($H138="","",S138-AB138)</f>
       </c>
     </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="G139" s="3"/>
@@ -7147,7 +7147,7 @@
         <f>IF($H139="","",S139-AB139)</f>
       </c>
     </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="G140" s="3"/>
@@ -7193,7 +7193,7 @@
         <f>IF($H140="","",S140-AB140)</f>
       </c>
     </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="G141" s="3"/>
@@ -7239,7 +7239,7 @@
         <f>IF($H141="","",S141-AB141)</f>
       </c>
     </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="G142" s="3"/>
@@ -7285,7 +7285,7 @@
         <f>IF($H142="","",S142-AB142)</f>
       </c>
     </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="G143" s="3"/>
@@ -7331,7 +7331,7 @@
         <f>IF($H143="","",S143-AB143)</f>
       </c>
     </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="G144" s="3"/>
@@ -7377,7 +7377,7 @@
         <f>IF($H144="","",S144-AB144)</f>
       </c>
     </row>
-    <row r="145" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="G145" s="3"/>
@@ -7423,7 +7423,7 @@
         <f>IF($H145="","",S145-AB145)</f>
       </c>
     </row>
-    <row r="146" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="G146" s="3"/>
@@ -7469,7 +7469,7 @@
         <f>IF($H146="","",S146-AB146)</f>
       </c>
     </row>
-    <row r="147" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="G147" s="3"/>
@@ -7515,7 +7515,7 @@
         <f>IF($H147="","",S147-AB147)</f>
       </c>
     </row>
-    <row r="148" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="G148" s="3"/>
@@ -7561,7 +7561,7 @@
         <f>IF($H148="","",S148-AB148)</f>
       </c>
     </row>
-    <row r="149" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="G149" s="3"/>
@@ -7607,7 +7607,7 @@
         <f>IF($H149="","",S149-AB149)</f>
       </c>
     </row>
-    <row r="150" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="G150" s="3"/>
@@ -7653,7 +7653,7 @@
         <f>IF($H150="","",S150-AB150)</f>
       </c>
     </row>
-    <row r="151" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="G151" s="3"/>
@@ -7699,7 +7699,7 @@
         <f>IF($H151="","",S151-AB151)</f>
       </c>
     </row>
-    <row r="152" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="G152" s="3"/>
@@ -7745,7 +7745,7 @@
         <f>IF($H152="","",S152-AB152)</f>
       </c>
     </row>
-    <row r="153" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="G153" s="3"/>
@@ -7791,7 +7791,7 @@
         <f>IF($H153="","",S153-AB153)</f>
       </c>
     </row>
-    <row r="154" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="G154" s="3"/>
@@ -7837,7 +7837,7 @@
         <f>IF($H154="","",S154-AB154)</f>
       </c>
     </row>
-    <row r="155" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="G155" s="3"/>
@@ -7883,7 +7883,7 @@
         <f>IF($H155="","",S155-AB155)</f>
       </c>
     </row>
-    <row r="156" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="G156" s="3"/>
@@ -7929,7 +7929,7 @@
         <f>IF($H156="","",S156-AB156)</f>
       </c>
     </row>
-    <row r="157" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="G157" s="3"/>
@@ -7975,7 +7975,7 @@
         <f>IF($H157="","",S157-AB157)</f>
       </c>
     </row>
-    <row r="158" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="G158" s="3"/>
@@ -8021,7 +8021,7 @@
         <f>IF($H158="","",S158-AB158)</f>
       </c>
     </row>
-    <row r="159" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="G159" s="3"/>
@@ -8067,7 +8067,7 @@
         <f>IF($H159="","",S159-AB159)</f>
       </c>
     </row>
-    <row r="160" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="G160" s="3"/>
@@ -8113,7 +8113,7 @@
         <f>IF($H160="","",S160-AB160)</f>
       </c>
     </row>
-    <row r="161" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="G161" s="3"/>
@@ -8159,7 +8159,7 @@
         <f>IF($H161="","",S161-AB161)</f>
       </c>
     </row>
-    <row r="162" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="G162" s="3"/>
@@ -8205,7 +8205,7 @@
         <f>IF($H162="","",S162-AB162)</f>
       </c>
     </row>
-    <row r="163" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="G163" s="3"/>
@@ -8251,7 +8251,7 @@
         <f>IF($H163="","",S163-AB163)</f>
       </c>
     </row>
-    <row r="164" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="G164" s="3"/>
@@ -8297,7 +8297,7 @@
         <f>IF($H164="","",S164-AB164)</f>
       </c>
     </row>
-    <row r="165" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="G165" s="3"/>
@@ -8343,7 +8343,7 @@
         <f>IF($H165="","",S165-AB165)</f>
       </c>
     </row>
-    <row r="166" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="G166" s="3"/>
@@ -8389,7 +8389,7 @@
         <f>IF($H166="","",S166-AB166)</f>
       </c>
     </row>
-    <row r="167" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="G167" s="3"/>
@@ -8435,7 +8435,7 @@
         <f>IF($H167="","",S167-AB167)</f>
       </c>
     </row>
-    <row r="168" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="G168" s="3"/>
@@ -8481,7 +8481,7 @@
         <f>IF($H168="","",S168-AB168)</f>
       </c>
     </row>
-    <row r="169" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="G169" s="3"/>
@@ -8527,7 +8527,7 @@
         <f>IF($H169="","",S169-AB169)</f>
       </c>
     </row>
-    <row r="170" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="G170" s="3"/>
@@ -8573,7 +8573,7 @@
         <f>IF($H170="","",S170-AB170)</f>
       </c>
     </row>
-    <row r="171" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="G171" s="3"/>
@@ -8619,7 +8619,7 @@
         <f>IF($H171="","",S171-AB171)</f>
       </c>
     </row>
-    <row r="172" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="G172" s="3"/>
@@ -8665,7 +8665,7 @@
         <f>IF($H172="","",S172-AB172)</f>
       </c>
     </row>
-    <row r="173" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="G173" s="3"/>
@@ -8711,7 +8711,7 @@
         <f>IF($H173="","",S173-AB173)</f>
       </c>
     </row>
-    <row r="174" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="G174" s="3"/>
@@ -8757,7 +8757,7 @@
         <f>IF($H174="","",S174-AB174)</f>
       </c>
     </row>
-    <row r="175" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="G175" s="3"/>
@@ -8803,7 +8803,7 @@
         <f>IF($H175="","",S175-AB175)</f>
       </c>
     </row>
-    <row r="176" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="G176" s="3"/>
@@ -8849,7 +8849,7 @@
         <f>IF($H176="","",S176-AB176)</f>
       </c>
     </row>
-    <row r="177" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="G177" s="3"/>
@@ -8895,7 +8895,7 @@
         <f>IF($H177="","",S177-AB177)</f>
       </c>
     </row>
-    <row r="178" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="G178" s="3"/>
@@ -8941,7 +8941,7 @@
         <f>IF($H178="","",S178-AB178)</f>
       </c>
     </row>
-    <row r="179" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="G179" s="3"/>
@@ -8987,7 +8987,7 @@
         <f>IF($H179="","",S179-AB179)</f>
       </c>
     </row>
-    <row r="180" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="G180" s="3"/>
@@ -9033,7 +9033,7 @@
         <f>IF($H180="","",S180-AB180)</f>
       </c>
     </row>
-    <row r="181" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="G181" s="3"/>
@@ -9079,7 +9079,7 @@
         <f>IF($H181="","",S181-AB181)</f>
       </c>
     </row>
-    <row r="182" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="G182" s="3"/>
@@ -9125,7 +9125,7 @@
         <f>IF($H182="","",S182-AB182)</f>
       </c>
     </row>
-    <row r="183" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="G183" s="3"/>
@@ -9171,7 +9171,7 @@
         <f>IF($H183="","",S183-AB183)</f>
       </c>
     </row>
-    <row r="184" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="G184" s="3"/>
@@ -9217,7 +9217,7 @@
         <f>IF($H184="","",S184-AB184)</f>
       </c>
     </row>
-    <row r="185" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="G185" s="3"/>
@@ -9263,7 +9263,7 @@
         <f>IF($H185="","",S185-AB185)</f>
       </c>
     </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="G186" s="3"/>
@@ -9309,7 +9309,7 @@
         <f>IF($H186="","",S186-AB186)</f>
       </c>
     </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="G187" s="3"/>
@@ -9355,7 +9355,7 @@
         <f>IF($H187="","",S187-AB187)</f>
       </c>
     </row>
-    <row r="188" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="G188" s="3"/>
@@ -9401,7 +9401,7 @@
         <f>IF($H188="","",S188-AB188)</f>
       </c>
     </row>
-    <row r="189" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="G189" s="3"/>
@@ -9447,7 +9447,7 @@
         <f>IF($H189="","",S189-AB189)</f>
       </c>
     </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="G190" s="3"/>
@@ -9493,7 +9493,7 @@
         <f>IF($H190="","",S190-AB190)</f>
       </c>
     </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="G191" s="3"/>
@@ -9539,7 +9539,7 @@
         <f>IF($H191="","",S191-AB191)</f>
       </c>
     </row>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="G192" s="3"/>
@@ -9585,7 +9585,7 @@
         <f>IF($H192="","",S192-AB192)</f>
       </c>
     </row>
-    <row r="193" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="G193" s="3"/>
@@ -9631,7 +9631,7 @@
         <f>IF($H193="","",S193-AB193)</f>
       </c>
     </row>
-    <row r="194" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="G194" s="3"/>
@@ -9677,7 +9677,7 @@
         <f>IF($H194="","",S194-AB194)</f>
       </c>
     </row>
-    <row r="195" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="G195" s="3"/>
@@ -9723,7 +9723,7 @@
         <f>IF($H195="","",S195-AB195)</f>
       </c>
     </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="G196" s="3"/>
@@ -9769,7 +9769,7 @@
         <f>IF($H196="","",S196-AB196)</f>
       </c>
     </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="G197" s="3"/>
@@ -9815,7 +9815,7 @@
         <f>IF($H197="","",S197-AB197)</f>
       </c>
     </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="G198" s="3"/>
@@ -9861,7 +9861,7 @@
         <f>IF($H198="","",S198-AB198)</f>
       </c>
     </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="G199" s="3"/>
@@ -9907,7 +9907,7 @@
         <f>IF($H199="","",S199-AB199)</f>
       </c>
     </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="G200" s="3"/>
@@ -9953,7 +9953,7 @@
         <f>IF($H200="","",S200-AB200)</f>
       </c>
     </row>
-    <row r="201" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="G201" s="3"/>
@@ -9999,7 +9999,7 @@
         <f>IF($H201="","",S201-AB201)</f>
       </c>
     </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="G202" s="3"/>

--- a/public/templates/SALES_AMAZON_TEMPLATE.xlsx
+++ b/public/templates/SALES_AMAZON_TEMPLATE.xlsx
@@ -71,7 +71,7 @@
     <t>P. VAT</t>
   </si>
   <si>
-    <t>Accessories</t>
+    <t>Acc</t>
   </si>
   <si>
     <t>Total VAT</t>

--- a/public/templates/SALES_AMAZON_TEMPLATE.xlsx
+++ b/public/templates/SALES_AMAZON_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -87,6 +87,18 @@
   </si>
   <si>
     <t>Postage Loss</t>
+  </si>
+  <si>
+    <t>Fees Kept</t>
+  </si>
+  <si>
+    <t>Repair Cost</t>
+  </si>
+  <si>
+    <t>Supplier Credit</t>
+  </si>
+  <si>
+    <t>Return Cost</t>
   </si>
   <si>
     <t>Net GP £</t>
@@ -589,74 +601,74 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -667,10 +679,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE203"/>
+  <dimension ref="A1:AI203"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -764,31 +776,43 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46235.5</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -833,19 +857,19 @@
         <f>L2-M2-N2-O2-P2-Q2-R2-S2-T2</f>
       </c>
       <c r="W2" s="3">
-        <f>(V2-Y2)/J2*100</f>
+        <f>(V2-AC2)/J2*100</f>
       </c>
       <c r="X2" s="3">
         <f>M2-U2</f>
       </c>
-      <c r="Z2" s="3">
-        <f>V2-Y2</f>
-      </c>
-      <c r="AE2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD2" s="3">
+        <f>V2-AC2</f>
+      </c>
+      <c r="AI2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="J3" s="3"/>
@@ -882,16 +906,16 @@
         <f>IF($K3="","",L3-M3-N3-O3-P3-Q3-R3-S3-T3)</f>
       </c>
       <c r="W3" s="3">
-        <f>IF($K3="","",(V3-Y3)/J3*100)</f>
+        <f>IF($K3="","",(V3-AC3)/J3*100)</f>
       </c>
       <c r="X3" s="3">
         <f>IF($K3="","",M3-U3)</f>
       </c>
-      <c r="Z3" s="3">
-        <f>IF($K3="","",V3-Y3)</f>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD3" s="3">
+        <f>IF($K3="","",V3-AC3)</f>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="J4" s="3"/>
@@ -928,16 +952,16 @@
         <f>IF($K4="","",L4-M4-N4-O4-P4-Q4-R4-S4-T4)</f>
       </c>
       <c r="W4" s="3">
-        <f>IF($K4="","",(V4-Y4)/J4*100)</f>
+        <f>IF($K4="","",(V4-AC4)/J4*100)</f>
       </c>
       <c r="X4" s="3">
         <f>IF($K4="","",M4-U4)</f>
       </c>
-      <c r="Z4" s="3">
-        <f>IF($K4="","",V4-Y4)</f>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD4" s="3">
+        <f>IF($K4="","",V4-AC4)</f>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="J5" s="3"/>
@@ -974,16 +998,16 @@
         <f>IF($K5="","",L5-M5-N5-O5-P5-Q5-R5-S5-T5)</f>
       </c>
       <c r="W5" s="3">
-        <f>IF($K5="","",(V5-Y5)/J5*100)</f>
+        <f>IF($K5="","",(V5-AC5)/J5*100)</f>
       </c>
       <c r="X5" s="3">
         <f>IF($K5="","",M5-U5)</f>
       </c>
-      <c r="Z5" s="3">
-        <f>IF($K5="","",V5-Y5)</f>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD5" s="3">
+        <f>IF($K5="","",V5-AC5)</f>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="J6" s="3"/>
@@ -1020,16 +1044,16 @@
         <f>IF($K6="","",L6-M6-N6-O6-P6-Q6-R6-S6-T6)</f>
       </c>
       <c r="W6" s="3">
-        <f>IF($K6="","",(V6-Y6)/J6*100)</f>
+        <f>IF($K6="","",(V6-AC6)/J6*100)</f>
       </c>
       <c r="X6" s="3">
         <f>IF($K6="","",M6-U6)</f>
       </c>
-      <c r="Z6" s="3">
-        <f>IF($K6="","",V6-Y6)</f>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD6" s="3">
+        <f>IF($K6="","",V6-AC6)</f>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="J7" s="3"/>
@@ -1066,16 +1090,16 @@
         <f>IF($K7="","",L7-M7-N7-O7-P7-Q7-R7-S7-T7)</f>
       </c>
       <c r="W7" s="3">
-        <f>IF($K7="","",(V7-Y7)/J7*100)</f>
+        <f>IF($K7="","",(V7-AC7)/J7*100)</f>
       </c>
       <c r="X7" s="3">
         <f>IF($K7="","",M7-U7)</f>
       </c>
-      <c r="Z7" s="3">
-        <f>IF($K7="","",V7-Y7)</f>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD7" s="3">
+        <f>IF($K7="","",V7-AC7)</f>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="J8" s="3"/>
@@ -1112,16 +1136,16 @@
         <f>IF($K8="","",L8-M8-N8-O8-P8-Q8-R8-S8-T8)</f>
       </c>
       <c r="W8" s="3">
-        <f>IF($K8="","",(V8-Y8)/J8*100)</f>
+        <f>IF($K8="","",(V8-AC8)/J8*100)</f>
       </c>
       <c r="X8" s="3">
         <f>IF($K8="","",M8-U8)</f>
       </c>
-      <c r="Z8" s="3">
-        <f>IF($K8="","",V8-Y8)</f>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD8" s="3">
+        <f>IF($K8="","",V8-AC8)</f>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="J9" s="3"/>
@@ -1158,16 +1182,16 @@
         <f>IF($K9="","",L9-M9-N9-O9-P9-Q9-R9-S9-T9)</f>
       </c>
       <c r="W9" s="3">
-        <f>IF($K9="","",(V9-Y9)/J9*100)</f>
+        <f>IF($K9="","",(V9-AC9)/J9*100)</f>
       </c>
       <c r="X9" s="3">
         <f>IF($K9="","",M9-U9)</f>
       </c>
-      <c r="Z9" s="3">
-        <f>IF($K9="","",V9-Y9)</f>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD9" s="3">
+        <f>IF($K9="","",V9-AC9)</f>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="J10" s="3"/>
@@ -1204,16 +1228,16 @@
         <f>IF($K10="","",L10-M10-N10-O10-P10-Q10-R10-S10-T10)</f>
       </c>
       <c r="W10" s="3">
-        <f>IF($K10="","",(V10-Y10)/J10*100)</f>
+        <f>IF($K10="","",(V10-AC10)/J10*100)</f>
       </c>
       <c r="X10" s="3">
         <f>IF($K10="","",M10-U10)</f>
       </c>
-      <c r="Z10" s="3">
-        <f>IF($K10="","",V10-Y10)</f>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD10" s="3">
+        <f>IF($K10="","",V10-AC10)</f>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="J11" s="3"/>
@@ -1250,16 +1274,16 @@
         <f>IF($K11="","",L11-M11-N11-O11-P11-Q11-R11-S11-T11)</f>
       </c>
       <c r="W11" s="3">
-        <f>IF($K11="","",(V11-Y11)/J11*100)</f>
+        <f>IF($K11="","",(V11-AC11)/J11*100)</f>
       </c>
       <c r="X11" s="3">
         <f>IF($K11="","",M11-U11)</f>
       </c>
-      <c r="Z11" s="3">
-        <f>IF($K11="","",V11-Y11)</f>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD11" s="3">
+        <f>IF($K11="","",V11-AC11)</f>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="J12" s="3"/>
@@ -1296,16 +1320,16 @@
         <f>IF($K12="","",L12-M12-N12-O12-P12-Q12-R12-S12-T12)</f>
       </c>
       <c r="W12" s="3">
-        <f>IF($K12="","",(V12-Y12)/J12*100)</f>
+        <f>IF($K12="","",(V12-AC12)/J12*100)</f>
       </c>
       <c r="X12" s="3">
         <f>IF($K12="","",M12-U12)</f>
       </c>
-      <c r="Z12" s="3">
-        <f>IF($K12="","",V12-Y12)</f>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD12" s="3">
+        <f>IF($K12="","",V12-AC12)</f>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="J13" s="3"/>
@@ -1342,16 +1366,16 @@
         <f>IF($K13="","",L13-M13-N13-O13-P13-Q13-R13-S13-T13)</f>
       </c>
       <c r="W13" s="3">
-        <f>IF($K13="","",(V13-Y13)/J13*100)</f>
+        <f>IF($K13="","",(V13-AC13)/J13*100)</f>
       </c>
       <c r="X13" s="3">
         <f>IF($K13="","",M13-U13)</f>
       </c>
-      <c r="Z13" s="3">
-        <f>IF($K13="","",V13-Y13)</f>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD13" s="3">
+        <f>IF($K13="","",V13-AC13)</f>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="J14" s="3"/>
@@ -1388,16 +1412,16 @@
         <f>IF($K14="","",L14-M14-N14-O14-P14-Q14-R14-S14-T14)</f>
       </c>
       <c r="W14" s="3">
-        <f>IF($K14="","",(V14-Y14)/J14*100)</f>
+        <f>IF($K14="","",(V14-AC14)/J14*100)</f>
       </c>
       <c r="X14" s="3">
         <f>IF($K14="","",M14-U14)</f>
       </c>
-      <c r="Z14" s="3">
-        <f>IF($K14="","",V14-Y14)</f>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD14" s="3">
+        <f>IF($K14="","",V14-AC14)</f>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="J15" s="3"/>
@@ -1434,16 +1458,16 @@
         <f>IF($K15="","",L15-M15-N15-O15-P15-Q15-R15-S15-T15)</f>
       </c>
       <c r="W15" s="3">
-        <f>IF($K15="","",(V15-Y15)/J15*100)</f>
+        <f>IF($K15="","",(V15-AC15)/J15*100)</f>
       </c>
       <c r="X15" s="3">
         <f>IF($K15="","",M15-U15)</f>
       </c>
-      <c r="Z15" s="3">
-        <f>IF($K15="","",V15-Y15)</f>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD15" s="3">
+        <f>IF($K15="","",V15-AC15)</f>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="J16" s="3"/>
@@ -1480,16 +1504,16 @@
         <f>IF($K16="","",L16-M16-N16-O16-P16-Q16-R16-S16-T16)</f>
       </c>
       <c r="W16" s="3">
-        <f>IF($K16="","",(V16-Y16)/J16*100)</f>
+        <f>IF($K16="","",(V16-AC16)/J16*100)</f>
       </c>
       <c r="X16" s="3">
         <f>IF($K16="","",M16-U16)</f>
       </c>
-      <c r="Z16" s="3">
-        <f>IF($K16="","",V16-Y16)</f>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD16" s="3">
+        <f>IF($K16="","",V16-AC16)</f>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="J17" s="3"/>
@@ -1526,16 +1550,16 @@
         <f>IF($K17="","",L17-M17-N17-O17-P17-Q17-R17-S17-T17)</f>
       </c>
       <c r="W17" s="3">
-        <f>IF($K17="","",(V17-Y17)/J17*100)</f>
+        <f>IF($K17="","",(V17-AC17)/J17*100)</f>
       </c>
       <c r="X17" s="3">
         <f>IF($K17="","",M17-U17)</f>
       </c>
-      <c r="Z17" s="3">
-        <f>IF($K17="","",V17-Y17)</f>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD17" s="3">
+        <f>IF($K17="","",V17-AC17)</f>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="J18" s="3"/>
@@ -1572,16 +1596,16 @@
         <f>IF($K18="","",L18-M18-N18-O18-P18-Q18-R18-S18-T18)</f>
       </c>
       <c r="W18" s="3">
-        <f>IF($K18="","",(V18-Y18)/J18*100)</f>
+        <f>IF($K18="","",(V18-AC18)/J18*100)</f>
       </c>
       <c r="X18" s="3">
         <f>IF($K18="","",M18-U18)</f>
       </c>
-      <c r="Z18" s="3">
-        <f>IF($K18="","",V18-Y18)</f>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD18" s="3">
+        <f>IF($K18="","",V18-AC18)</f>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="J19" s="3"/>
@@ -1618,16 +1642,16 @@
         <f>IF($K19="","",L19-M19-N19-O19-P19-Q19-R19-S19-T19)</f>
       </c>
       <c r="W19" s="3">
-        <f>IF($K19="","",(V19-Y19)/J19*100)</f>
+        <f>IF($K19="","",(V19-AC19)/J19*100)</f>
       </c>
       <c r="X19" s="3">
         <f>IF($K19="","",M19-U19)</f>
       </c>
-      <c r="Z19" s="3">
-        <f>IF($K19="","",V19-Y19)</f>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD19" s="3">
+        <f>IF($K19="","",V19-AC19)</f>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="J20" s="3"/>
@@ -1664,16 +1688,16 @@
         <f>IF($K20="","",L20-M20-N20-O20-P20-Q20-R20-S20-T20)</f>
       </c>
       <c r="W20" s="3">
-        <f>IF($K20="","",(V20-Y20)/J20*100)</f>
+        <f>IF($K20="","",(V20-AC20)/J20*100)</f>
       </c>
       <c r="X20" s="3">
         <f>IF($K20="","",M20-U20)</f>
       </c>
-      <c r="Z20" s="3">
-        <f>IF($K20="","",V20-Y20)</f>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD20" s="3">
+        <f>IF($K20="","",V20-AC20)</f>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="J21" s="3"/>
@@ -1710,16 +1734,16 @@
         <f>IF($K21="","",L21-M21-N21-O21-P21-Q21-R21-S21-T21)</f>
       </c>
       <c r="W21" s="3">
-        <f>IF($K21="","",(V21-Y21)/J21*100)</f>
+        <f>IF($K21="","",(V21-AC21)/J21*100)</f>
       </c>
       <c r="X21" s="3">
         <f>IF($K21="","",M21-U21)</f>
       </c>
-      <c r="Z21" s="3">
-        <f>IF($K21="","",V21-Y21)</f>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD21" s="3">
+        <f>IF($K21="","",V21-AC21)</f>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="J22" s="3"/>
@@ -1756,16 +1780,16 @@
         <f>IF($K22="","",L22-M22-N22-O22-P22-Q22-R22-S22-T22)</f>
       </c>
       <c r="W22" s="3">
-        <f>IF($K22="","",(V22-Y22)/J22*100)</f>
+        <f>IF($K22="","",(V22-AC22)/J22*100)</f>
       </c>
       <c r="X22" s="3">
         <f>IF($K22="","",M22-U22)</f>
       </c>
-      <c r="Z22" s="3">
-        <f>IF($K22="","",V22-Y22)</f>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD22" s="3">
+        <f>IF($K22="","",V22-AC22)</f>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="J23" s="3"/>
@@ -1802,16 +1826,16 @@
         <f>IF($K23="","",L23-M23-N23-O23-P23-Q23-R23-S23-T23)</f>
       </c>
       <c r="W23" s="3">
-        <f>IF($K23="","",(V23-Y23)/J23*100)</f>
+        <f>IF($K23="","",(V23-AC23)/J23*100)</f>
       </c>
       <c r="X23" s="3">
         <f>IF($K23="","",M23-U23)</f>
       </c>
-      <c r="Z23" s="3">
-        <f>IF($K23="","",V23-Y23)</f>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD23" s="3">
+        <f>IF($K23="","",V23-AC23)</f>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="J24" s="3"/>
@@ -1848,16 +1872,16 @@
         <f>IF($K24="","",L24-M24-N24-O24-P24-Q24-R24-S24-T24)</f>
       </c>
       <c r="W24" s="3">
-        <f>IF($K24="","",(V24-Y24)/J24*100)</f>
+        <f>IF($K24="","",(V24-AC24)/J24*100)</f>
       </c>
       <c r="X24" s="3">
         <f>IF($K24="","",M24-U24)</f>
       </c>
-      <c r="Z24" s="3">
-        <f>IF($K24="","",V24-Y24)</f>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD24" s="3">
+        <f>IF($K24="","",V24-AC24)</f>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="J25" s="3"/>
@@ -1894,16 +1918,16 @@
         <f>IF($K25="","",L25-M25-N25-O25-P25-Q25-R25-S25-T25)</f>
       </c>
       <c r="W25" s="3">
-        <f>IF($K25="","",(V25-Y25)/J25*100)</f>
+        <f>IF($K25="","",(V25-AC25)/J25*100)</f>
       </c>
       <c r="X25" s="3">
         <f>IF($K25="","",M25-U25)</f>
       </c>
-      <c r="Z25" s="3">
-        <f>IF($K25="","",V25-Y25)</f>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD25" s="3">
+        <f>IF($K25="","",V25-AC25)</f>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="J26" s="3"/>
@@ -1940,16 +1964,16 @@
         <f>IF($K26="","",L26-M26-N26-O26-P26-Q26-R26-S26-T26)</f>
       </c>
       <c r="W26" s="3">
-        <f>IF($K26="","",(V26-Y26)/J26*100)</f>
+        <f>IF($K26="","",(V26-AC26)/J26*100)</f>
       </c>
       <c r="X26" s="3">
         <f>IF($K26="","",M26-U26)</f>
       </c>
-      <c r="Z26" s="3">
-        <f>IF($K26="","",V26-Y26)</f>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD26" s="3">
+        <f>IF($K26="","",V26-AC26)</f>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="J27" s="3"/>
@@ -1986,16 +2010,16 @@
         <f>IF($K27="","",L27-M27-N27-O27-P27-Q27-R27-S27-T27)</f>
       </c>
       <c r="W27" s="3">
-        <f>IF($K27="","",(V27-Y27)/J27*100)</f>
+        <f>IF($K27="","",(V27-AC27)/J27*100)</f>
       </c>
       <c r="X27" s="3">
         <f>IF($K27="","",M27-U27)</f>
       </c>
-      <c r="Z27" s="3">
-        <f>IF($K27="","",V27-Y27)</f>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD27" s="3">
+        <f>IF($K27="","",V27-AC27)</f>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="J28" s="3"/>
@@ -2032,16 +2056,16 @@
         <f>IF($K28="","",L28-M28-N28-O28-P28-Q28-R28-S28-T28)</f>
       </c>
       <c r="W28" s="3">
-        <f>IF($K28="","",(V28-Y28)/J28*100)</f>
+        <f>IF($K28="","",(V28-AC28)/J28*100)</f>
       </c>
       <c r="X28" s="3">
         <f>IF($K28="","",M28-U28)</f>
       </c>
-      <c r="Z28" s="3">
-        <f>IF($K28="","",V28-Y28)</f>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD28" s="3">
+        <f>IF($K28="","",V28-AC28)</f>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="J29" s="3"/>
@@ -2078,16 +2102,16 @@
         <f>IF($K29="","",L29-M29-N29-O29-P29-Q29-R29-S29-T29)</f>
       </c>
       <c r="W29" s="3">
-        <f>IF($K29="","",(V29-Y29)/J29*100)</f>
+        <f>IF($K29="","",(V29-AC29)/J29*100)</f>
       </c>
       <c r="X29" s="3">
         <f>IF($K29="","",M29-U29)</f>
       </c>
-      <c r="Z29" s="3">
-        <f>IF($K29="","",V29-Y29)</f>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD29" s="3">
+        <f>IF($K29="","",V29-AC29)</f>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="J30" s="3"/>
@@ -2124,16 +2148,16 @@
         <f>IF($K30="","",L30-M30-N30-O30-P30-Q30-R30-S30-T30)</f>
       </c>
       <c r="W30" s="3">
-        <f>IF($K30="","",(V30-Y30)/J30*100)</f>
+        <f>IF($K30="","",(V30-AC30)/J30*100)</f>
       </c>
       <c r="X30" s="3">
         <f>IF($K30="","",M30-U30)</f>
       </c>
-      <c r="Z30" s="3">
-        <f>IF($K30="","",V30-Y30)</f>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD30" s="3">
+        <f>IF($K30="","",V30-AC30)</f>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="J31" s="3"/>
@@ -2170,16 +2194,16 @@
         <f>IF($K31="","",L31-M31-N31-O31-P31-Q31-R31-S31-T31)</f>
       </c>
       <c r="W31" s="3">
-        <f>IF($K31="","",(V31-Y31)/J31*100)</f>
+        <f>IF($K31="","",(V31-AC31)/J31*100)</f>
       </c>
       <c r="X31" s="3">
         <f>IF($K31="","",M31-U31)</f>
       </c>
-      <c r="Z31" s="3">
-        <f>IF($K31="","",V31-Y31)</f>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD31" s="3">
+        <f>IF($K31="","",V31-AC31)</f>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="J32" s="3"/>
@@ -2216,16 +2240,16 @@
         <f>IF($K32="","",L32-M32-N32-O32-P32-Q32-R32-S32-T32)</f>
       </c>
       <c r="W32" s="3">
-        <f>IF($K32="","",(V32-Y32)/J32*100)</f>
+        <f>IF($K32="","",(V32-AC32)/J32*100)</f>
       </c>
       <c r="X32" s="3">
         <f>IF($K32="","",M32-U32)</f>
       </c>
-      <c r="Z32" s="3">
-        <f>IF($K32="","",V32-Y32)</f>
-      </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD32" s="3">
+        <f>IF($K32="","",V32-AC32)</f>
+      </c>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="J33" s="3"/>
@@ -2262,16 +2286,16 @@
         <f>IF($K33="","",L33-M33-N33-O33-P33-Q33-R33-S33-T33)</f>
       </c>
       <c r="W33" s="3">
-        <f>IF($K33="","",(V33-Y33)/J33*100)</f>
+        <f>IF($K33="","",(V33-AC33)/J33*100)</f>
       </c>
       <c r="X33" s="3">
         <f>IF($K33="","",M33-U33)</f>
       </c>
-      <c r="Z33" s="3">
-        <f>IF($K33="","",V33-Y33)</f>
-      </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD33" s="3">
+        <f>IF($K33="","",V33-AC33)</f>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="J34" s="3"/>
@@ -2308,16 +2332,16 @@
         <f>IF($K34="","",L34-M34-N34-O34-P34-Q34-R34-S34-T34)</f>
       </c>
       <c r="W34" s="3">
-        <f>IF($K34="","",(V34-Y34)/J34*100)</f>
+        <f>IF($K34="","",(V34-AC34)/J34*100)</f>
       </c>
       <c r="X34" s="3">
         <f>IF($K34="","",M34-U34)</f>
       </c>
-      <c r="Z34" s="3">
-        <f>IF($K34="","",V34-Y34)</f>
-      </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD34" s="3">
+        <f>IF($K34="","",V34-AC34)</f>
+      </c>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="J35" s="3"/>
@@ -2354,16 +2378,16 @@
         <f>IF($K35="","",L35-M35-N35-O35-P35-Q35-R35-S35-T35)</f>
       </c>
       <c r="W35" s="3">
-        <f>IF($K35="","",(V35-Y35)/J35*100)</f>
+        <f>IF($K35="","",(V35-AC35)/J35*100)</f>
       </c>
       <c r="X35" s="3">
         <f>IF($K35="","",M35-U35)</f>
       </c>
-      <c r="Z35" s="3">
-        <f>IF($K35="","",V35-Y35)</f>
-      </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD35" s="3">
+        <f>IF($K35="","",V35-AC35)</f>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="J36" s="3"/>
@@ -2400,16 +2424,16 @@
         <f>IF($K36="","",L36-M36-N36-O36-P36-Q36-R36-S36-T36)</f>
       </c>
       <c r="W36" s="3">
-        <f>IF($K36="","",(V36-Y36)/J36*100)</f>
+        <f>IF($K36="","",(V36-AC36)/J36*100)</f>
       </c>
       <c r="X36" s="3">
         <f>IF($K36="","",M36-U36)</f>
       </c>
-      <c r="Z36" s="3">
-        <f>IF($K36="","",V36-Y36)</f>
-      </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD36" s="3">
+        <f>IF($K36="","",V36-AC36)</f>
+      </c>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="J37" s="3"/>
@@ -2446,16 +2470,16 @@
         <f>IF($K37="","",L37-M37-N37-O37-P37-Q37-R37-S37-T37)</f>
       </c>
       <c r="W37" s="3">
-        <f>IF($K37="","",(V37-Y37)/J37*100)</f>
+        <f>IF($K37="","",(V37-AC37)/J37*100)</f>
       </c>
       <c r="X37" s="3">
         <f>IF($K37="","",M37-U37)</f>
       </c>
-      <c r="Z37" s="3">
-        <f>IF($K37="","",V37-Y37)</f>
-      </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD37" s="3">
+        <f>IF($K37="","",V37-AC37)</f>
+      </c>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="J38" s="3"/>
@@ -2492,16 +2516,16 @@
         <f>IF($K38="","",L38-M38-N38-O38-P38-Q38-R38-S38-T38)</f>
       </c>
       <c r="W38" s="3">
-        <f>IF($K38="","",(V38-Y38)/J38*100)</f>
+        <f>IF($K38="","",(V38-AC38)/J38*100)</f>
       </c>
       <c r="X38" s="3">
         <f>IF($K38="","",M38-U38)</f>
       </c>
-      <c r="Z38" s="3">
-        <f>IF($K38="","",V38-Y38)</f>
-      </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD38" s="3">
+        <f>IF($K38="","",V38-AC38)</f>
+      </c>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="J39" s="3"/>
@@ -2538,16 +2562,16 @@
         <f>IF($K39="","",L39-M39-N39-O39-P39-Q39-R39-S39-T39)</f>
       </c>
       <c r="W39" s="3">
-        <f>IF($K39="","",(V39-Y39)/J39*100)</f>
+        <f>IF($K39="","",(V39-AC39)/J39*100)</f>
       </c>
       <c r="X39" s="3">
         <f>IF($K39="","",M39-U39)</f>
       </c>
-      <c r="Z39" s="3">
-        <f>IF($K39="","",V39-Y39)</f>
-      </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD39" s="3">
+        <f>IF($K39="","",V39-AC39)</f>
+      </c>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="J40" s="3"/>
@@ -2584,16 +2608,16 @@
         <f>IF($K40="","",L40-M40-N40-O40-P40-Q40-R40-S40-T40)</f>
       </c>
       <c r="W40" s="3">
-        <f>IF($K40="","",(V40-Y40)/J40*100)</f>
+        <f>IF($K40="","",(V40-AC40)/J40*100)</f>
       </c>
       <c r="X40" s="3">
         <f>IF($K40="","",M40-U40)</f>
       </c>
-      <c r="Z40" s="3">
-        <f>IF($K40="","",V40-Y40)</f>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD40" s="3">
+        <f>IF($K40="","",V40-AC40)</f>
+      </c>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="J41" s="3"/>
@@ -2630,16 +2654,16 @@
         <f>IF($K41="","",L41-M41-N41-O41-P41-Q41-R41-S41-T41)</f>
       </c>
       <c r="W41" s="3">
-        <f>IF($K41="","",(V41-Y41)/J41*100)</f>
+        <f>IF($K41="","",(V41-AC41)/J41*100)</f>
       </c>
       <c r="X41" s="3">
         <f>IF($K41="","",M41-U41)</f>
       </c>
-      <c r="Z41" s="3">
-        <f>IF($K41="","",V41-Y41)</f>
-      </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD41" s="3">
+        <f>IF($K41="","",V41-AC41)</f>
+      </c>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="J42" s="3"/>
@@ -2676,16 +2700,16 @@
         <f>IF($K42="","",L42-M42-N42-O42-P42-Q42-R42-S42-T42)</f>
       </c>
       <c r="W42" s="3">
-        <f>IF($K42="","",(V42-Y42)/J42*100)</f>
+        <f>IF($K42="","",(V42-AC42)/J42*100)</f>
       </c>
       <c r="X42" s="3">
         <f>IF($K42="","",M42-U42)</f>
       </c>
-      <c r="Z42" s="3">
-        <f>IF($K42="","",V42-Y42)</f>
-      </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD42" s="3">
+        <f>IF($K42="","",V42-AC42)</f>
+      </c>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="J43" s="3"/>
@@ -2722,16 +2746,16 @@
         <f>IF($K43="","",L43-M43-N43-O43-P43-Q43-R43-S43-T43)</f>
       </c>
       <c r="W43" s="3">
-        <f>IF($K43="","",(V43-Y43)/J43*100)</f>
+        <f>IF($K43="","",(V43-AC43)/J43*100)</f>
       </c>
       <c r="X43" s="3">
         <f>IF($K43="","",M43-U43)</f>
       </c>
-      <c r="Z43" s="3">
-        <f>IF($K43="","",V43-Y43)</f>
-      </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD43" s="3">
+        <f>IF($K43="","",V43-AC43)</f>
+      </c>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="J44" s="3"/>
@@ -2768,16 +2792,16 @@
         <f>IF($K44="","",L44-M44-N44-O44-P44-Q44-R44-S44-T44)</f>
       </c>
       <c r="W44" s="3">
-        <f>IF($K44="","",(V44-Y44)/J44*100)</f>
+        <f>IF($K44="","",(V44-AC44)/J44*100)</f>
       </c>
       <c r="X44" s="3">
         <f>IF($K44="","",M44-U44)</f>
       </c>
-      <c r="Z44" s="3">
-        <f>IF($K44="","",V44-Y44)</f>
-      </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD44" s="3">
+        <f>IF($K44="","",V44-AC44)</f>
+      </c>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="J45" s="3"/>
@@ -2814,16 +2838,16 @@
         <f>IF($K45="","",L45-M45-N45-O45-P45-Q45-R45-S45-T45)</f>
       </c>
       <c r="W45" s="3">
-        <f>IF($K45="","",(V45-Y45)/J45*100)</f>
+        <f>IF($K45="","",(V45-AC45)/J45*100)</f>
       </c>
       <c r="X45" s="3">
         <f>IF($K45="","",M45-U45)</f>
       </c>
-      <c r="Z45" s="3">
-        <f>IF($K45="","",V45-Y45)</f>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD45" s="3">
+        <f>IF($K45="","",V45-AC45)</f>
+      </c>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="J46" s="3"/>
@@ -2860,16 +2884,16 @@
         <f>IF($K46="","",L46-M46-N46-O46-P46-Q46-R46-S46-T46)</f>
       </c>
       <c r="W46" s="3">
-        <f>IF($K46="","",(V46-Y46)/J46*100)</f>
+        <f>IF($K46="","",(V46-AC46)/J46*100)</f>
       </c>
       <c r="X46" s="3">
         <f>IF($K46="","",M46-U46)</f>
       </c>
-      <c r="Z46" s="3">
-        <f>IF($K46="","",V46-Y46)</f>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD46" s="3">
+        <f>IF($K46="","",V46-AC46)</f>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="J47" s="3"/>
@@ -2906,16 +2930,16 @@
         <f>IF($K47="","",L47-M47-N47-O47-P47-Q47-R47-S47-T47)</f>
       </c>
       <c r="W47" s="3">
-        <f>IF($K47="","",(V47-Y47)/J47*100)</f>
+        <f>IF($K47="","",(V47-AC47)/J47*100)</f>
       </c>
       <c r="X47" s="3">
         <f>IF($K47="","",M47-U47)</f>
       </c>
-      <c r="Z47" s="3">
-        <f>IF($K47="","",V47-Y47)</f>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD47" s="3">
+        <f>IF($K47="","",V47-AC47)</f>
+      </c>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="J48" s="3"/>
@@ -2952,16 +2976,16 @@
         <f>IF($K48="","",L48-M48-N48-O48-P48-Q48-R48-S48-T48)</f>
       </c>
       <c r="W48" s="3">
-        <f>IF($K48="","",(V48-Y48)/J48*100)</f>
+        <f>IF($K48="","",(V48-AC48)/J48*100)</f>
       </c>
       <c r="X48" s="3">
         <f>IF($K48="","",M48-U48)</f>
       </c>
-      <c r="Z48" s="3">
-        <f>IF($K48="","",V48-Y48)</f>
-      </c>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD48" s="3">
+        <f>IF($K48="","",V48-AC48)</f>
+      </c>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="J49" s="3"/>
@@ -2998,16 +3022,16 @@
         <f>IF($K49="","",L49-M49-N49-O49-P49-Q49-R49-S49-T49)</f>
       </c>
       <c r="W49" s="3">
-        <f>IF($K49="","",(V49-Y49)/J49*100)</f>
+        <f>IF($K49="","",(V49-AC49)/J49*100)</f>
       </c>
       <c r="X49" s="3">
         <f>IF($K49="","",M49-U49)</f>
       </c>
-      <c r="Z49" s="3">
-        <f>IF($K49="","",V49-Y49)</f>
-      </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD49" s="3">
+        <f>IF($K49="","",V49-AC49)</f>
+      </c>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="J50" s="3"/>
@@ -3044,16 +3068,16 @@
         <f>IF($K50="","",L50-M50-N50-O50-P50-Q50-R50-S50-T50)</f>
       </c>
       <c r="W50" s="3">
-        <f>IF($K50="","",(V50-Y50)/J50*100)</f>
+        <f>IF($K50="","",(V50-AC50)/J50*100)</f>
       </c>
       <c r="X50" s="3">
         <f>IF($K50="","",M50-U50)</f>
       </c>
-      <c r="Z50" s="3">
-        <f>IF($K50="","",V50-Y50)</f>
-      </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD50" s="3">
+        <f>IF($K50="","",V50-AC50)</f>
+      </c>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="J51" s="3"/>
@@ -3090,16 +3114,16 @@
         <f>IF($K51="","",L51-M51-N51-O51-P51-Q51-R51-S51-T51)</f>
       </c>
       <c r="W51" s="3">
-        <f>IF($K51="","",(V51-Y51)/J51*100)</f>
+        <f>IF($K51="","",(V51-AC51)/J51*100)</f>
       </c>
       <c r="X51" s="3">
         <f>IF($K51="","",M51-U51)</f>
       </c>
-      <c r="Z51" s="3">
-        <f>IF($K51="","",V51-Y51)</f>
-      </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD51" s="3">
+        <f>IF($K51="","",V51-AC51)</f>
+      </c>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="J52" s="3"/>
@@ -3136,16 +3160,16 @@
         <f>IF($K52="","",L52-M52-N52-O52-P52-Q52-R52-S52-T52)</f>
       </c>
       <c r="W52" s="3">
-        <f>IF($K52="","",(V52-Y52)/J52*100)</f>
+        <f>IF($K52="","",(V52-AC52)/J52*100)</f>
       </c>
       <c r="X52" s="3">
         <f>IF($K52="","",M52-U52)</f>
       </c>
-      <c r="Z52" s="3">
-        <f>IF($K52="","",V52-Y52)</f>
-      </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD52" s="3">
+        <f>IF($K52="","",V52-AC52)</f>
+      </c>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="J53" s="3"/>
@@ -3182,16 +3206,16 @@
         <f>IF($K53="","",L53-M53-N53-O53-P53-Q53-R53-S53-T53)</f>
       </c>
       <c r="W53" s="3">
-        <f>IF($K53="","",(V53-Y53)/J53*100)</f>
+        <f>IF($K53="","",(V53-AC53)/J53*100)</f>
       </c>
       <c r="X53" s="3">
         <f>IF($K53="","",M53-U53)</f>
       </c>
-      <c r="Z53" s="3">
-        <f>IF($K53="","",V53-Y53)</f>
-      </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD53" s="3">
+        <f>IF($K53="","",V53-AC53)</f>
+      </c>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="J54" s="3"/>
@@ -3228,16 +3252,16 @@
         <f>IF($K54="","",L54-M54-N54-O54-P54-Q54-R54-S54-T54)</f>
       </c>
       <c r="W54" s="3">
-        <f>IF($K54="","",(V54-Y54)/J54*100)</f>
+        <f>IF($K54="","",(V54-AC54)/J54*100)</f>
       </c>
       <c r="X54" s="3">
         <f>IF($K54="","",M54-U54)</f>
       </c>
-      <c r="Z54" s="3">
-        <f>IF($K54="","",V54-Y54)</f>
-      </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD54" s="3">
+        <f>IF($K54="","",V54-AC54)</f>
+      </c>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="J55" s="3"/>
@@ -3274,16 +3298,16 @@
         <f>IF($K55="","",L55-M55-N55-O55-P55-Q55-R55-S55-T55)</f>
       </c>
       <c r="W55" s="3">
-        <f>IF($K55="","",(V55-Y55)/J55*100)</f>
+        <f>IF($K55="","",(V55-AC55)/J55*100)</f>
       </c>
       <c r="X55" s="3">
         <f>IF($K55="","",M55-U55)</f>
       </c>
-      <c r="Z55" s="3">
-        <f>IF($K55="","",V55-Y55)</f>
-      </c>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD55" s="3">
+        <f>IF($K55="","",V55-AC55)</f>
+      </c>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="J56" s="3"/>
@@ -3320,16 +3344,16 @@
         <f>IF($K56="","",L56-M56-N56-O56-P56-Q56-R56-S56-T56)</f>
       </c>
       <c r="W56" s="3">
-        <f>IF($K56="","",(V56-Y56)/J56*100)</f>
+        <f>IF($K56="","",(V56-AC56)/J56*100)</f>
       </c>
       <c r="X56" s="3">
         <f>IF($K56="","",M56-U56)</f>
       </c>
-      <c r="Z56" s="3">
-        <f>IF($K56="","",V56-Y56)</f>
-      </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD56" s="3">
+        <f>IF($K56="","",V56-AC56)</f>
+      </c>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="J57" s="3"/>
@@ -3366,16 +3390,16 @@
         <f>IF($K57="","",L57-M57-N57-O57-P57-Q57-R57-S57-T57)</f>
       </c>
       <c r="W57" s="3">
-        <f>IF($K57="","",(V57-Y57)/J57*100)</f>
+        <f>IF($K57="","",(V57-AC57)/J57*100)</f>
       </c>
       <c r="X57" s="3">
         <f>IF($K57="","",M57-U57)</f>
       </c>
-      <c r="Z57" s="3">
-        <f>IF($K57="","",V57-Y57)</f>
-      </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD57" s="3">
+        <f>IF($K57="","",V57-AC57)</f>
+      </c>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="J58" s="3"/>
@@ -3412,16 +3436,16 @@
         <f>IF($K58="","",L58-M58-N58-O58-P58-Q58-R58-S58-T58)</f>
       </c>
       <c r="W58" s="3">
-        <f>IF($K58="","",(V58-Y58)/J58*100)</f>
+        <f>IF($K58="","",(V58-AC58)/J58*100)</f>
       </c>
       <c r="X58" s="3">
         <f>IF($K58="","",M58-U58)</f>
       </c>
-      <c r="Z58" s="3">
-        <f>IF($K58="","",V58-Y58)</f>
-      </c>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD58" s="3">
+        <f>IF($K58="","",V58-AC58)</f>
+      </c>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="J59" s="3"/>
@@ -3458,16 +3482,16 @@
         <f>IF($K59="","",L59-M59-N59-O59-P59-Q59-R59-S59-T59)</f>
       </c>
       <c r="W59" s="3">
-        <f>IF($K59="","",(V59-Y59)/J59*100)</f>
+        <f>IF($K59="","",(V59-AC59)/J59*100)</f>
       </c>
       <c r="X59" s="3">
         <f>IF($K59="","",M59-U59)</f>
       </c>
-      <c r="Z59" s="3">
-        <f>IF($K59="","",V59-Y59)</f>
-      </c>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD59" s="3">
+        <f>IF($K59="","",V59-AC59)</f>
+      </c>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="J60" s="3"/>
@@ -3504,16 +3528,16 @@
         <f>IF($K60="","",L60-M60-N60-O60-P60-Q60-R60-S60-T60)</f>
       </c>
       <c r="W60" s="3">
-        <f>IF($K60="","",(V60-Y60)/J60*100)</f>
+        <f>IF($K60="","",(V60-AC60)/J60*100)</f>
       </c>
       <c r="X60" s="3">
         <f>IF($K60="","",M60-U60)</f>
       </c>
-      <c r="Z60" s="3">
-        <f>IF($K60="","",V60-Y60)</f>
-      </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD60" s="3">
+        <f>IF($K60="","",V60-AC60)</f>
+      </c>
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="J61" s="3"/>
@@ -3550,16 +3574,16 @@
         <f>IF($K61="","",L61-M61-N61-O61-P61-Q61-R61-S61-T61)</f>
       </c>
       <c r="W61" s="3">
-        <f>IF($K61="","",(V61-Y61)/J61*100)</f>
+        <f>IF($K61="","",(V61-AC61)/J61*100)</f>
       </c>
       <c r="X61" s="3">
         <f>IF($K61="","",M61-U61)</f>
       </c>
-      <c r="Z61" s="3">
-        <f>IF($K61="","",V61-Y61)</f>
-      </c>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD61" s="3">
+        <f>IF($K61="","",V61-AC61)</f>
+      </c>
+    </row>
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="J62" s="3"/>
@@ -3596,16 +3620,16 @@
         <f>IF($K62="","",L62-M62-N62-O62-P62-Q62-R62-S62-T62)</f>
       </c>
       <c r="W62" s="3">
-        <f>IF($K62="","",(V62-Y62)/J62*100)</f>
+        <f>IF($K62="","",(V62-AC62)/J62*100)</f>
       </c>
       <c r="X62" s="3">
         <f>IF($K62="","",M62-U62)</f>
       </c>
-      <c r="Z62" s="3">
-        <f>IF($K62="","",V62-Y62)</f>
-      </c>
-    </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD62" s="3">
+        <f>IF($K62="","",V62-AC62)</f>
+      </c>
+    </row>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="J63" s="3"/>
@@ -3642,16 +3666,16 @@
         <f>IF($K63="","",L63-M63-N63-O63-P63-Q63-R63-S63-T63)</f>
       </c>
       <c r="W63" s="3">
-        <f>IF($K63="","",(V63-Y63)/J63*100)</f>
+        <f>IF($K63="","",(V63-AC63)/J63*100)</f>
       </c>
       <c r="X63" s="3">
         <f>IF($K63="","",M63-U63)</f>
       </c>
-      <c r="Z63" s="3">
-        <f>IF($K63="","",V63-Y63)</f>
-      </c>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD63" s="3">
+        <f>IF($K63="","",V63-AC63)</f>
+      </c>
+    </row>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="J64" s="3"/>
@@ -3688,16 +3712,16 @@
         <f>IF($K64="","",L64-M64-N64-O64-P64-Q64-R64-S64-T64)</f>
       </c>
       <c r="W64" s="3">
-        <f>IF($K64="","",(V64-Y64)/J64*100)</f>
+        <f>IF($K64="","",(V64-AC64)/J64*100)</f>
       </c>
       <c r="X64" s="3">
         <f>IF($K64="","",M64-U64)</f>
       </c>
-      <c r="Z64" s="3">
-        <f>IF($K64="","",V64-Y64)</f>
-      </c>
-    </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD64" s="3">
+        <f>IF($K64="","",V64-AC64)</f>
+      </c>
+    </row>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="J65" s="3"/>
@@ -3734,16 +3758,16 @@
         <f>IF($K65="","",L65-M65-N65-O65-P65-Q65-R65-S65-T65)</f>
       </c>
       <c r="W65" s="3">
-        <f>IF($K65="","",(V65-Y65)/J65*100)</f>
+        <f>IF($K65="","",(V65-AC65)/J65*100)</f>
       </c>
       <c r="X65" s="3">
         <f>IF($K65="","",M65-U65)</f>
       </c>
-      <c r="Z65" s="3">
-        <f>IF($K65="","",V65-Y65)</f>
-      </c>
-    </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD65" s="3">
+        <f>IF($K65="","",V65-AC65)</f>
+      </c>
+    </row>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="J66" s="3"/>
@@ -3780,16 +3804,16 @@
         <f>IF($K66="","",L66-M66-N66-O66-P66-Q66-R66-S66-T66)</f>
       </c>
       <c r="W66" s="3">
-        <f>IF($K66="","",(V66-Y66)/J66*100)</f>
+        <f>IF($K66="","",(V66-AC66)/J66*100)</f>
       </c>
       <c r="X66" s="3">
         <f>IF($K66="","",M66-U66)</f>
       </c>
-      <c r="Z66" s="3">
-        <f>IF($K66="","",V66-Y66)</f>
-      </c>
-    </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD66" s="3">
+        <f>IF($K66="","",V66-AC66)</f>
+      </c>
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="J67" s="3"/>
@@ -3826,16 +3850,16 @@
         <f>IF($K67="","",L67-M67-N67-O67-P67-Q67-R67-S67-T67)</f>
       </c>
       <c r="W67" s="3">
-        <f>IF($K67="","",(V67-Y67)/J67*100)</f>
+        <f>IF($K67="","",(V67-AC67)/J67*100)</f>
       </c>
       <c r="X67" s="3">
         <f>IF($K67="","",M67-U67)</f>
       </c>
-      <c r="Z67" s="3">
-        <f>IF($K67="","",V67-Y67)</f>
-      </c>
-    </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD67" s="3">
+        <f>IF($K67="","",V67-AC67)</f>
+      </c>
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="J68" s="3"/>
@@ -3872,16 +3896,16 @@
         <f>IF($K68="","",L68-M68-N68-O68-P68-Q68-R68-S68-T68)</f>
       </c>
       <c r="W68" s="3">
-        <f>IF($K68="","",(V68-Y68)/J68*100)</f>
+        <f>IF($K68="","",(V68-AC68)/J68*100)</f>
       </c>
       <c r="X68" s="3">
         <f>IF($K68="","",M68-U68)</f>
       </c>
-      <c r="Z68" s="3">
-        <f>IF($K68="","",V68-Y68)</f>
-      </c>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD68" s="3">
+        <f>IF($K68="","",V68-AC68)</f>
+      </c>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="J69" s="3"/>
@@ -3918,16 +3942,16 @@
         <f>IF($K69="","",L69-M69-N69-O69-P69-Q69-R69-S69-T69)</f>
       </c>
       <c r="W69" s="3">
-        <f>IF($K69="","",(V69-Y69)/J69*100)</f>
+        <f>IF($K69="","",(V69-AC69)/J69*100)</f>
       </c>
       <c r="X69" s="3">
         <f>IF($K69="","",M69-U69)</f>
       </c>
-      <c r="Z69" s="3">
-        <f>IF($K69="","",V69-Y69)</f>
-      </c>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD69" s="3">
+        <f>IF($K69="","",V69-AC69)</f>
+      </c>
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="J70" s="3"/>
@@ -3964,16 +3988,16 @@
         <f>IF($K70="","",L70-M70-N70-O70-P70-Q70-R70-S70-T70)</f>
       </c>
       <c r="W70" s="3">
-        <f>IF($K70="","",(V70-Y70)/J70*100)</f>
+        <f>IF($K70="","",(V70-AC70)/J70*100)</f>
       </c>
       <c r="X70" s="3">
         <f>IF($K70="","",M70-U70)</f>
       </c>
-      <c r="Z70" s="3">
-        <f>IF($K70="","",V70-Y70)</f>
-      </c>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD70" s="3">
+        <f>IF($K70="","",V70-AC70)</f>
+      </c>
+    </row>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="J71" s="3"/>
@@ -4010,16 +4034,16 @@
         <f>IF($K71="","",L71-M71-N71-O71-P71-Q71-R71-S71-T71)</f>
       </c>
       <c r="W71" s="3">
-        <f>IF($K71="","",(V71-Y71)/J71*100)</f>
+        <f>IF($K71="","",(V71-AC71)/J71*100)</f>
       </c>
       <c r="X71" s="3">
         <f>IF($K71="","",M71-U71)</f>
       </c>
-      <c r="Z71" s="3">
-        <f>IF($K71="","",V71-Y71)</f>
-      </c>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD71" s="3">
+        <f>IF($K71="","",V71-AC71)</f>
+      </c>
+    </row>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="J72" s="3"/>
@@ -4056,16 +4080,16 @@
         <f>IF($K72="","",L72-M72-N72-O72-P72-Q72-R72-S72-T72)</f>
       </c>
       <c r="W72" s="3">
-        <f>IF($K72="","",(V72-Y72)/J72*100)</f>
+        <f>IF($K72="","",(V72-AC72)/J72*100)</f>
       </c>
       <c r="X72" s="3">
         <f>IF($K72="","",M72-U72)</f>
       </c>
-      <c r="Z72" s="3">
-        <f>IF($K72="","",V72-Y72)</f>
-      </c>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD72" s="3">
+        <f>IF($K72="","",V72-AC72)</f>
+      </c>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="J73" s="3"/>
@@ -4102,16 +4126,16 @@
         <f>IF($K73="","",L73-M73-N73-O73-P73-Q73-R73-S73-T73)</f>
       </c>
       <c r="W73" s="3">
-        <f>IF($K73="","",(V73-Y73)/J73*100)</f>
+        <f>IF($K73="","",(V73-AC73)/J73*100)</f>
       </c>
       <c r="X73" s="3">
         <f>IF($K73="","",M73-U73)</f>
       </c>
-      <c r="Z73" s="3">
-        <f>IF($K73="","",V73-Y73)</f>
-      </c>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD73" s="3">
+        <f>IF($K73="","",V73-AC73)</f>
+      </c>
+    </row>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="J74" s="3"/>
@@ -4148,16 +4172,16 @@
         <f>IF($K74="","",L74-M74-N74-O74-P74-Q74-R74-S74-T74)</f>
       </c>
       <c r="W74" s="3">
-        <f>IF($K74="","",(V74-Y74)/J74*100)</f>
+        <f>IF($K74="","",(V74-AC74)/J74*100)</f>
       </c>
       <c r="X74" s="3">
         <f>IF($K74="","",M74-U74)</f>
       </c>
-      <c r="Z74" s="3">
-        <f>IF($K74="","",V74-Y74)</f>
-      </c>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD74" s="3">
+        <f>IF($K74="","",V74-AC74)</f>
+      </c>
+    </row>
+    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="J75" s="3"/>
@@ -4194,16 +4218,16 @@
         <f>IF($K75="","",L75-M75-N75-O75-P75-Q75-R75-S75-T75)</f>
       </c>
       <c r="W75" s="3">
-        <f>IF($K75="","",(V75-Y75)/J75*100)</f>
+        <f>IF($K75="","",(V75-AC75)/J75*100)</f>
       </c>
       <c r="X75" s="3">
         <f>IF($K75="","",M75-U75)</f>
       </c>
-      <c r="Z75" s="3">
-        <f>IF($K75="","",V75-Y75)</f>
-      </c>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD75" s="3">
+        <f>IF($K75="","",V75-AC75)</f>
+      </c>
+    </row>
+    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="J76" s="3"/>
@@ -4240,16 +4264,16 @@
         <f>IF($K76="","",L76-M76-N76-O76-P76-Q76-R76-S76-T76)</f>
       </c>
       <c r="W76" s="3">
-        <f>IF($K76="","",(V76-Y76)/J76*100)</f>
+        <f>IF($K76="","",(V76-AC76)/J76*100)</f>
       </c>
       <c r="X76" s="3">
         <f>IF($K76="","",M76-U76)</f>
       </c>
-      <c r="Z76" s="3">
-        <f>IF($K76="","",V76-Y76)</f>
-      </c>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD76" s="3">
+        <f>IF($K76="","",V76-AC76)</f>
+      </c>
+    </row>
+    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="J77" s="3"/>
@@ -4286,16 +4310,16 @@
         <f>IF($K77="","",L77-M77-N77-O77-P77-Q77-R77-S77-T77)</f>
       </c>
       <c r="W77" s="3">
-        <f>IF($K77="","",(V77-Y77)/J77*100)</f>
+        <f>IF($K77="","",(V77-AC77)/J77*100)</f>
       </c>
       <c r="X77" s="3">
         <f>IF($K77="","",M77-U77)</f>
       </c>
-      <c r="Z77" s="3">
-        <f>IF($K77="","",V77-Y77)</f>
-      </c>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD77" s="3">
+        <f>IF($K77="","",V77-AC77)</f>
+      </c>
+    </row>
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="J78" s="3"/>
@@ -4332,16 +4356,16 @@
         <f>IF($K78="","",L78-M78-N78-O78-P78-Q78-R78-S78-T78)</f>
       </c>
       <c r="W78" s="3">
-        <f>IF($K78="","",(V78-Y78)/J78*100)</f>
+        <f>IF($K78="","",(V78-AC78)/J78*100)</f>
       </c>
       <c r="X78" s="3">
         <f>IF($K78="","",M78-U78)</f>
       </c>
-      <c r="Z78" s="3">
-        <f>IF($K78="","",V78-Y78)</f>
-      </c>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD78" s="3">
+        <f>IF($K78="","",V78-AC78)</f>
+      </c>
+    </row>
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="J79" s="3"/>
@@ -4378,16 +4402,16 @@
         <f>IF($K79="","",L79-M79-N79-O79-P79-Q79-R79-S79-T79)</f>
       </c>
       <c r="W79" s="3">
-        <f>IF($K79="","",(V79-Y79)/J79*100)</f>
+        <f>IF($K79="","",(V79-AC79)/J79*100)</f>
       </c>
       <c r="X79" s="3">
         <f>IF($K79="","",M79-U79)</f>
       </c>
-      <c r="Z79" s="3">
-        <f>IF($K79="","",V79-Y79)</f>
-      </c>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD79" s="3">
+        <f>IF($K79="","",V79-AC79)</f>
+      </c>
+    </row>
+    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="J80" s="3"/>
@@ -4424,16 +4448,16 @@
         <f>IF($K80="","",L80-M80-N80-O80-P80-Q80-R80-S80-T80)</f>
       </c>
       <c r="W80" s="3">
-        <f>IF($K80="","",(V80-Y80)/J80*100)</f>
+        <f>IF($K80="","",(V80-AC80)/J80*100)</f>
       </c>
       <c r="X80" s="3">
         <f>IF($K80="","",M80-U80)</f>
       </c>
-      <c r="Z80" s="3">
-        <f>IF($K80="","",V80-Y80)</f>
-      </c>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD80" s="3">
+        <f>IF($K80="","",V80-AC80)</f>
+      </c>
+    </row>
+    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="J81" s="3"/>
@@ -4470,16 +4494,16 @@
         <f>IF($K81="","",L81-M81-N81-O81-P81-Q81-R81-S81-T81)</f>
       </c>
       <c r="W81" s="3">
-        <f>IF($K81="","",(V81-Y81)/J81*100)</f>
+        <f>IF($K81="","",(V81-AC81)/J81*100)</f>
       </c>
       <c r="X81" s="3">
         <f>IF($K81="","",M81-U81)</f>
       </c>
-      <c r="Z81" s="3">
-        <f>IF($K81="","",V81-Y81)</f>
-      </c>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD81" s="3">
+        <f>IF($K81="","",V81-AC81)</f>
+      </c>
+    </row>
+    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="J82" s="3"/>
@@ -4516,16 +4540,16 @@
         <f>IF($K82="","",L82-M82-N82-O82-P82-Q82-R82-S82-T82)</f>
       </c>
       <c r="W82" s="3">
-        <f>IF($K82="","",(V82-Y82)/J82*100)</f>
+        <f>IF($K82="","",(V82-AC82)/J82*100)</f>
       </c>
       <c r="X82" s="3">
         <f>IF($K82="","",M82-U82)</f>
       </c>
-      <c r="Z82" s="3">
-        <f>IF($K82="","",V82-Y82)</f>
-      </c>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD82" s="3">
+        <f>IF($K82="","",V82-AC82)</f>
+      </c>
+    </row>
+    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="J83" s="3"/>
@@ -4562,16 +4586,16 @@
         <f>IF($K83="","",L83-M83-N83-O83-P83-Q83-R83-S83-T83)</f>
       </c>
       <c r="W83" s="3">
-        <f>IF($K83="","",(V83-Y83)/J83*100)</f>
+        <f>IF($K83="","",(V83-AC83)/J83*100)</f>
       </c>
       <c r="X83" s="3">
         <f>IF($K83="","",M83-U83)</f>
       </c>
-      <c r="Z83" s="3">
-        <f>IF($K83="","",V83-Y83)</f>
-      </c>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD83" s="3">
+        <f>IF($K83="","",V83-AC83)</f>
+      </c>
+    </row>
+    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="J84" s="3"/>
@@ -4608,16 +4632,16 @@
         <f>IF($K84="","",L84-M84-N84-O84-P84-Q84-R84-S84-T84)</f>
       </c>
       <c r="W84" s="3">
-        <f>IF($K84="","",(V84-Y84)/J84*100)</f>
+        <f>IF($K84="","",(V84-AC84)/J84*100)</f>
       </c>
       <c r="X84" s="3">
         <f>IF($K84="","",M84-U84)</f>
       </c>
-      <c r="Z84" s="3">
-        <f>IF($K84="","",V84-Y84)</f>
-      </c>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD84" s="3">
+        <f>IF($K84="","",V84-AC84)</f>
+      </c>
+    </row>
+    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="J85" s="3"/>
@@ -4654,16 +4678,16 @@
         <f>IF($K85="","",L85-M85-N85-O85-P85-Q85-R85-S85-T85)</f>
       </c>
       <c r="W85" s="3">
-        <f>IF($K85="","",(V85-Y85)/J85*100)</f>
+        <f>IF($K85="","",(V85-AC85)/J85*100)</f>
       </c>
       <c r="X85" s="3">
         <f>IF($K85="","",M85-U85)</f>
       </c>
-      <c r="Z85" s="3">
-        <f>IF($K85="","",V85-Y85)</f>
-      </c>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD85" s="3">
+        <f>IF($K85="","",V85-AC85)</f>
+      </c>
+    </row>
+    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="J86" s="3"/>
@@ -4700,16 +4724,16 @@
         <f>IF($K86="","",L86-M86-N86-O86-P86-Q86-R86-S86-T86)</f>
       </c>
       <c r="W86" s="3">
-        <f>IF($K86="","",(V86-Y86)/J86*100)</f>
+        <f>IF($K86="","",(V86-AC86)/J86*100)</f>
       </c>
       <c r="X86" s="3">
         <f>IF($K86="","",M86-U86)</f>
       </c>
-      <c r="Z86" s="3">
-        <f>IF($K86="","",V86-Y86)</f>
-      </c>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD86" s="3">
+        <f>IF($K86="","",V86-AC86)</f>
+      </c>
+    </row>
+    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="J87" s="3"/>
@@ -4746,16 +4770,16 @@
         <f>IF($K87="","",L87-M87-N87-O87-P87-Q87-R87-S87-T87)</f>
       </c>
       <c r="W87" s="3">
-        <f>IF($K87="","",(V87-Y87)/J87*100)</f>
+        <f>IF($K87="","",(V87-AC87)/J87*100)</f>
       </c>
       <c r="X87" s="3">
         <f>IF($K87="","",M87-U87)</f>
       </c>
-      <c r="Z87" s="3">
-        <f>IF($K87="","",V87-Y87)</f>
-      </c>
-    </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD87" s="3">
+        <f>IF($K87="","",V87-AC87)</f>
+      </c>
+    </row>
+    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="J88" s="3"/>
@@ -4792,16 +4816,16 @@
         <f>IF($K88="","",L88-M88-N88-O88-P88-Q88-R88-S88-T88)</f>
       </c>
       <c r="W88" s="3">
-        <f>IF($K88="","",(V88-Y88)/J88*100)</f>
+        <f>IF($K88="","",(V88-AC88)/J88*100)</f>
       </c>
       <c r="X88" s="3">
         <f>IF($K88="","",M88-U88)</f>
       </c>
-      <c r="Z88" s="3">
-        <f>IF($K88="","",V88-Y88)</f>
-      </c>
-    </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD88" s="3">
+        <f>IF($K88="","",V88-AC88)</f>
+      </c>
+    </row>
+    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="J89" s="3"/>
@@ -4838,16 +4862,16 @@
         <f>IF($K89="","",L89-M89-N89-O89-P89-Q89-R89-S89-T89)</f>
       </c>
       <c r="W89" s="3">
-        <f>IF($K89="","",(V89-Y89)/J89*100)</f>
+        <f>IF($K89="","",(V89-AC89)/J89*100)</f>
       </c>
       <c r="X89" s="3">
         <f>IF($K89="","",M89-U89)</f>
       </c>
-      <c r="Z89" s="3">
-        <f>IF($K89="","",V89-Y89)</f>
-      </c>
-    </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD89" s="3">
+        <f>IF($K89="","",V89-AC89)</f>
+      </c>
+    </row>
+    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="J90" s="3"/>
@@ -4884,16 +4908,16 @@
         <f>IF($K90="","",L90-M90-N90-O90-P90-Q90-R90-S90-T90)</f>
       </c>
       <c r="W90" s="3">
-        <f>IF($K90="","",(V90-Y90)/J90*100)</f>
+        <f>IF($K90="","",(V90-AC90)/J90*100)</f>
       </c>
       <c r="X90" s="3">
         <f>IF($K90="","",M90-U90)</f>
       </c>
-      <c r="Z90" s="3">
-        <f>IF($K90="","",V90-Y90)</f>
-      </c>
-    </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD90" s="3">
+        <f>IF($K90="","",V90-AC90)</f>
+      </c>
+    </row>
+    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="J91" s="3"/>
@@ -4930,16 +4954,16 @@
         <f>IF($K91="","",L91-M91-N91-O91-P91-Q91-R91-S91-T91)</f>
       </c>
       <c r="W91" s="3">
-        <f>IF($K91="","",(V91-Y91)/J91*100)</f>
+        <f>IF($K91="","",(V91-AC91)/J91*100)</f>
       </c>
       <c r="X91" s="3">
         <f>IF($K91="","",M91-U91)</f>
       </c>
-      <c r="Z91" s="3">
-        <f>IF($K91="","",V91-Y91)</f>
-      </c>
-    </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD91" s="3">
+        <f>IF($K91="","",V91-AC91)</f>
+      </c>
+    </row>
+    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="J92" s="3"/>
@@ -4976,16 +5000,16 @@
         <f>IF($K92="","",L92-M92-N92-O92-P92-Q92-R92-S92-T92)</f>
       </c>
       <c r="W92" s="3">
-        <f>IF($K92="","",(V92-Y92)/J92*100)</f>
+        <f>IF($K92="","",(V92-AC92)/J92*100)</f>
       </c>
       <c r="X92" s="3">
         <f>IF($K92="","",M92-U92)</f>
       </c>
-      <c r="Z92" s="3">
-        <f>IF($K92="","",V92-Y92)</f>
-      </c>
-    </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD92" s="3">
+        <f>IF($K92="","",V92-AC92)</f>
+      </c>
+    </row>
+    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="J93" s="3"/>
@@ -5022,16 +5046,16 @@
         <f>IF($K93="","",L93-M93-N93-O93-P93-Q93-R93-S93-T93)</f>
       </c>
       <c r="W93" s="3">
-        <f>IF($K93="","",(V93-Y93)/J93*100)</f>
+        <f>IF($K93="","",(V93-AC93)/J93*100)</f>
       </c>
       <c r="X93" s="3">
         <f>IF($K93="","",M93-U93)</f>
       </c>
-      <c r="Z93" s="3">
-        <f>IF($K93="","",V93-Y93)</f>
-      </c>
-    </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD93" s="3">
+        <f>IF($K93="","",V93-AC93)</f>
+      </c>
+    </row>
+    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="J94" s="3"/>
@@ -5068,16 +5092,16 @@
         <f>IF($K94="","",L94-M94-N94-O94-P94-Q94-R94-S94-T94)</f>
       </c>
       <c r="W94" s="3">
-        <f>IF($K94="","",(V94-Y94)/J94*100)</f>
+        <f>IF($K94="","",(V94-AC94)/J94*100)</f>
       </c>
       <c r="X94" s="3">
         <f>IF($K94="","",M94-U94)</f>
       </c>
-      <c r="Z94" s="3">
-        <f>IF($K94="","",V94-Y94)</f>
-      </c>
-    </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD94" s="3">
+        <f>IF($K94="","",V94-AC94)</f>
+      </c>
+    </row>
+    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="J95" s="3"/>
@@ -5114,16 +5138,16 @@
         <f>IF($K95="","",L95-M95-N95-O95-P95-Q95-R95-S95-T95)</f>
       </c>
       <c r="W95" s="3">
-        <f>IF($K95="","",(V95-Y95)/J95*100)</f>
+        <f>IF($K95="","",(V95-AC95)/J95*100)</f>
       </c>
       <c r="X95" s="3">
         <f>IF($K95="","",M95-U95)</f>
       </c>
-      <c r="Z95" s="3">
-        <f>IF($K95="","",V95-Y95)</f>
-      </c>
-    </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD95" s="3">
+        <f>IF($K95="","",V95-AC95)</f>
+      </c>
+    </row>
+    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="J96" s="3"/>
@@ -5160,16 +5184,16 @@
         <f>IF($K96="","",L96-M96-N96-O96-P96-Q96-R96-S96-T96)</f>
       </c>
       <c r="W96" s="3">
-        <f>IF($K96="","",(V96-Y96)/J96*100)</f>
+        <f>IF($K96="","",(V96-AC96)/J96*100)</f>
       </c>
       <c r="X96" s="3">
         <f>IF($K96="","",M96-U96)</f>
       </c>
-      <c r="Z96" s="3">
-        <f>IF($K96="","",V96-Y96)</f>
-      </c>
-    </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD96" s="3">
+        <f>IF($K96="","",V96-AC96)</f>
+      </c>
+    </row>
+    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="J97" s="3"/>
@@ -5206,16 +5230,16 @@
         <f>IF($K97="","",L97-M97-N97-O97-P97-Q97-R97-S97-T97)</f>
       </c>
       <c r="W97" s="3">
-        <f>IF($K97="","",(V97-Y97)/J97*100)</f>
+        <f>IF($K97="","",(V97-AC97)/J97*100)</f>
       </c>
       <c r="X97" s="3">
         <f>IF($K97="","",M97-U97)</f>
       </c>
-      <c r="Z97" s="3">
-        <f>IF($K97="","",V97-Y97)</f>
-      </c>
-    </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD97" s="3">
+        <f>IF($K97="","",V97-AC97)</f>
+      </c>
+    </row>
+    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="J98" s="3"/>
@@ -5252,16 +5276,16 @@
         <f>IF($K98="","",L98-M98-N98-O98-P98-Q98-R98-S98-T98)</f>
       </c>
       <c r="W98" s="3">
-        <f>IF($K98="","",(V98-Y98)/J98*100)</f>
+        <f>IF($K98="","",(V98-AC98)/J98*100)</f>
       </c>
       <c r="X98" s="3">
         <f>IF($K98="","",M98-U98)</f>
       </c>
-      <c r="Z98" s="3">
-        <f>IF($K98="","",V98-Y98)</f>
-      </c>
-    </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD98" s="3">
+        <f>IF($K98="","",V98-AC98)</f>
+      </c>
+    </row>
+    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="J99" s="3"/>
@@ -5298,16 +5322,16 @@
         <f>IF($K99="","",L99-M99-N99-O99-P99-Q99-R99-S99-T99)</f>
       </c>
       <c r="W99" s="3">
-        <f>IF($K99="","",(V99-Y99)/J99*100)</f>
+        <f>IF($K99="","",(V99-AC99)/J99*100)</f>
       </c>
       <c r="X99" s="3">
         <f>IF($K99="","",M99-U99)</f>
       </c>
-      <c r="Z99" s="3">
-        <f>IF($K99="","",V99-Y99)</f>
-      </c>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD99" s="3">
+        <f>IF($K99="","",V99-AC99)</f>
+      </c>
+    </row>
+    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="J100" s="3"/>
@@ -5344,16 +5368,16 @@
         <f>IF($K100="","",L100-M100-N100-O100-P100-Q100-R100-S100-T100)</f>
       </c>
       <c r="W100" s="3">
-        <f>IF($K100="","",(V100-Y100)/J100*100)</f>
+        <f>IF($K100="","",(V100-AC100)/J100*100)</f>
       </c>
       <c r="X100" s="3">
         <f>IF($K100="","",M100-U100)</f>
       </c>
-      <c r="Z100" s="3">
-        <f>IF($K100="","",V100-Y100)</f>
-      </c>
-    </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD100" s="3">
+        <f>IF($K100="","",V100-AC100)</f>
+      </c>
+    </row>
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="J101" s="3"/>
@@ -5390,16 +5414,16 @@
         <f>IF($K101="","",L101-M101-N101-O101-P101-Q101-R101-S101-T101)</f>
       </c>
       <c r="W101" s="3">
-        <f>IF($K101="","",(V101-Y101)/J101*100)</f>
+        <f>IF($K101="","",(V101-AC101)/J101*100)</f>
       </c>
       <c r="X101" s="3">
         <f>IF($K101="","",M101-U101)</f>
       </c>
-      <c r="Z101" s="3">
-        <f>IF($K101="","",V101-Y101)</f>
-      </c>
-    </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD101" s="3">
+        <f>IF($K101="","",V101-AC101)</f>
+      </c>
+    </row>
+    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="J102" s="3"/>
@@ -5436,16 +5460,16 @@
         <f>IF($K102="","",L102-M102-N102-O102-P102-Q102-R102-S102-T102)</f>
       </c>
       <c r="W102" s="3">
-        <f>IF($K102="","",(V102-Y102)/J102*100)</f>
+        <f>IF($K102="","",(V102-AC102)/J102*100)</f>
       </c>
       <c r="X102" s="3">
         <f>IF($K102="","",M102-U102)</f>
       </c>
-      <c r="Z102" s="3">
-        <f>IF($K102="","",V102-Y102)</f>
-      </c>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD102" s="3">
+        <f>IF($K102="","",V102-AC102)</f>
+      </c>
+    </row>
+    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="J103" s="3"/>
@@ -5482,16 +5506,16 @@
         <f>IF($K103="","",L103-M103-N103-O103-P103-Q103-R103-S103-T103)</f>
       </c>
       <c r="W103" s="3">
-        <f>IF($K103="","",(V103-Y103)/J103*100)</f>
+        <f>IF($K103="","",(V103-AC103)/J103*100)</f>
       </c>
       <c r="X103" s="3">
         <f>IF($K103="","",M103-U103)</f>
       </c>
-      <c r="Z103" s="3">
-        <f>IF($K103="","",V103-Y103)</f>
-      </c>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD103" s="3">
+        <f>IF($K103="","",V103-AC103)</f>
+      </c>
+    </row>
+    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="J104" s="3"/>
@@ -5528,16 +5552,16 @@
         <f>IF($K104="","",L104-M104-N104-O104-P104-Q104-R104-S104-T104)</f>
       </c>
       <c r="W104" s="3">
-        <f>IF($K104="","",(V104-Y104)/J104*100)</f>
+        <f>IF($K104="","",(V104-AC104)/J104*100)</f>
       </c>
       <c r="X104" s="3">
         <f>IF($K104="","",M104-U104)</f>
       </c>
-      <c r="Z104" s="3">
-        <f>IF($K104="","",V104-Y104)</f>
-      </c>
-    </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD104" s="3">
+        <f>IF($K104="","",V104-AC104)</f>
+      </c>
+    </row>
+    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="J105" s="3"/>
@@ -5574,16 +5598,16 @@
         <f>IF($K105="","",L105-M105-N105-O105-P105-Q105-R105-S105-T105)</f>
       </c>
       <c r="W105" s="3">
-        <f>IF($K105="","",(V105-Y105)/J105*100)</f>
+        <f>IF($K105="","",(V105-AC105)/J105*100)</f>
       </c>
       <c r="X105" s="3">
         <f>IF($K105="","",M105-U105)</f>
       </c>
-      <c r="Z105" s="3">
-        <f>IF($K105="","",V105-Y105)</f>
-      </c>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD105" s="3">
+        <f>IF($K105="","",V105-AC105)</f>
+      </c>
+    </row>
+    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="J106" s="3"/>
@@ -5620,16 +5644,16 @@
         <f>IF($K106="","",L106-M106-N106-O106-P106-Q106-R106-S106-T106)</f>
       </c>
       <c r="W106" s="3">
-        <f>IF($K106="","",(V106-Y106)/J106*100)</f>
+        <f>IF($K106="","",(V106-AC106)/J106*100)</f>
       </c>
       <c r="X106" s="3">
         <f>IF($K106="","",M106-U106)</f>
       </c>
-      <c r="Z106" s="3">
-        <f>IF($K106="","",V106-Y106)</f>
-      </c>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD106" s="3">
+        <f>IF($K106="","",V106-AC106)</f>
+      </c>
+    </row>
+    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="J107" s="3"/>
@@ -5666,16 +5690,16 @@
         <f>IF($K107="","",L107-M107-N107-O107-P107-Q107-R107-S107-T107)</f>
       </c>
       <c r="W107" s="3">
-        <f>IF($K107="","",(V107-Y107)/J107*100)</f>
+        <f>IF($K107="","",(V107-AC107)/J107*100)</f>
       </c>
       <c r="X107" s="3">
         <f>IF($K107="","",M107-U107)</f>
       </c>
-      <c r="Z107" s="3">
-        <f>IF($K107="","",V107-Y107)</f>
-      </c>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD107" s="3">
+        <f>IF($K107="","",V107-AC107)</f>
+      </c>
+    </row>
+    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="J108" s="3"/>
@@ -5712,16 +5736,16 @@
         <f>IF($K108="","",L108-M108-N108-O108-P108-Q108-R108-S108-T108)</f>
       </c>
       <c r="W108" s="3">
-        <f>IF($K108="","",(V108-Y108)/J108*100)</f>
+        <f>IF($K108="","",(V108-AC108)/J108*100)</f>
       </c>
       <c r="X108" s="3">
         <f>IF($K108="","",M108-U108)</f>
       </c>
-      <c r="Z108" s="3">
-        <f>IF($K108="","",V108-Y108)</f>
-      </c>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD108" s="3">
+        <f>IF($K108="","",V108-AC108)</f>
+      </c>
+    </row>
+    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="J109" s="3"/>
@@ -5758,16 +5782,16 @@
         <f>IF($K109="","",L109-M109-N109-O109-P109-Q109-R109-S109-T109)</f>
       </c>
       <c r="W109" s="3">
-        <f>IF($K109="","",(V109-Y109)/J109*100)</f>
+        <f>IF($K109="","",(V109-AC109)/J109*100)</f>
       </c>
       <c r="X109" s="3">
         <f>IF($K109="","",M109-U109)</f>
       </c>
-      <c r="Z109" s="3">
-        <f>IF($K109="","",V109-Y109)</f>
-      </c>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD109" s="3">
+        <f>IF($K109="","",V109-AC109)</f>
+      </c>
+    </row>
+    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="J110" s="3"/>
@@ -5804,16 +5828,16 @@
         <f>IF($K110="","",L110-M110-N110-O110-P110-Q110-R110-S110-T110)</f>
       </c>
       <c r="W110" s="3">
-        <f>IF($K110="","",(V110-Y110)/J110*100)</f>
+        <f>IF($K110="","",(V110-AC110)/J110*100)</f>
       </c>
       <c r="X110" s="3">
         <f>IF($K110="","",M110-U110)</f>
       </c>
-      <c r="Z110" s="3">
-        <f>IF($K110="","",V110-Y110)</f>
-      </c>
-    </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD110" s="3">
+        <f>IF($K110="","",V110-AC110)</f>
+      </c>
+    </row>
+    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="J111" s="3"/>
@@ -5850,16 +5874,16 @@
         <f>IF($K111="","",L111-M111-N111-O111-P111-Q111-R111-S111-T111)</f>
       </c>
       <c r="W111" s="3">
-        <f>IF($K111="","",(V111-Y111)/J111*100)</f>
+        <f>IF($K111="","",(V111-AC111)/J111*100)</f>
       </c>
       <c r="X111" s="3">
         <f>IF($K111="","",M111-U111)</f>
       </c>
-      <c r="Z111" s="3">
-        <f>IF($K111="","",V111-Y111)</f>
-      </c>
-    </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD111" s="3">
+        <f>IF($K111="","",V111-AC111)</f>
+      </c>
+    </row>
+    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="J112" s="3"/>
@@ -5896,16 +5920,16 @@
         <f>IF($K112="","",L112-M112-N112-O112-P112-Q112-R112-S112-T112)</f>
       </c>
       <c r="W112" s="3">
-        <f>IF($K112="","",(V112-Y112)/J112*100)</f>
+        <f>IF($K112="","",(V112-AC112)/J112*100)</f>
       </c>
       <c r="X112" s="3">
         <f>IF($K112="","",M112-U112)</f>
       </c>
-      <c r="Z112" s="3">
-        <f>IF($K112="","",V112-Y112)</f>
-      </c>
-    </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD112" s="3">
+        <f>IF($K112="","",V112-AC112)</f>
+      </c>
+    </row>
+    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="J113" s="3"/>
@@ -5942,16 +5966,16 @@
         <f>IF($K113="","",L113-M113-N113-O113-P113-Q113-R113-S113-T113)</f>
       </c>
       <c r="W113" s="3">
-        <f>IF($K113="","",(V113-Y113)/J113*100)</f>
+        <f>IF($K113="","",(V113-AC113)/J113*100)</f>
       </c>
       <c r="X113" s="3">
         <f>IF($K113="","",M113-U113)</f>
       </c>
-      <c r="Z113" s="3">
-        <f>IF($K113="","",V113-Y113)</f>
-      </c>
-    </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD113" s="3">
+        <f>IF($K113="","",V113-AC113)</f>
+      </c>
+    </row>
+    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="J114" s="3"/>
@@ -5988,16 +6012,16 @@
         <f>IF($K114="","",L114-M114-N114-O114-P114-Q114-R114-S114-T114)</f>
       </c>
       <c r="W114" s="3">
-        <f>IF($K114="","",(V114-Y114)/J114*100)</f>
+        <f>IF($K114="","",(V114-AC114)/J114*100)</f>
       </c>
       <c r="X114" s="3">
         <f>IF($K114="","",M114-U114)</f>
       </c>
-      <c r="Z114" s="3">
-        <f>IF($K114="","",V114-Y114)</f>
-      </c>
-    </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD114" s="3">
+        <f>IF($K114="","",V114-AC114)</f>
+      </c>
+    </row>
+    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="J115" s="3"/>
@@ -6034,16 +6058,16 @@
         <f>IF($K115="","",L115-M115-N115-O115-P115-Q115-R115-S115-T115)</f>
       </c>
       <c r="W115" s="3">
-        <f>IF($K115="","",(V115-Y115)/J115*100)</f>
+        <f>IF($K115="","",(V115-AC115)/J115*100)</f>
       </c>
       <c r="X115" s="3">
         <f>IF($K115="","",M115-U115)</f>
       </c>
-      <c r="Z115" s="3">
-        <f>IF($K115="","",V115-Y115)</f>
-      </c>
-    </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD115" s="3">
+        <f>IF($K115="","",V115-AC115)</f>
+      </c>
+    </row>
+    <row r="116" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="J116" s="3"/>
@@ -6080,16 +6104,16 @@
         <f>IF($K116="","",L116-M116-N116-O116-P116-Q116-R116-S116-T116)</f>
       </c>
       <c r="W116" s="3">
-        <f>IF($K116="","",(V116-Y116)/J116*100)</f>
+        <f>IF($K116="","",(V116-AC116)/J116*100)</f>
       </c>
       <c r="X116" s="3">
         <f>IF($K116="","",M116-U116)</f>
       </c>
-      <c r="Z116" s="3">
-        <f>IF($K116="","",V116-Y116)</f>
-      </c>
-    </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD116" s="3">
+        <f>IF($K116="","",V116-AC116)</f>
+      </c>
+    </row>
+    <row r="117" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="J117" s="3"/>
@@ -6126,16 +6150,16 @@
         <f>IF($K117="","",L117-M117-N117-O117-P117-Q117-R117-S117-T117)</f>
       </c>
       <c r="W117" s="3">
-        <f>IF($K117="","",(V117-Y117)/J117*100)</f>
+        <f>IF($K117="","",(V117-AC117)/J117*100)</f>
       </c>
       <c r="X117" s="3">
         <f>IF($K117="","",M117-U117)</f>
       </c>
-      <c r="Z117" s="3">
-        <f>IF($K117="","",V117-Y117)</f>
-      </c>
-    </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD117" s="3">
+        <f>IF($K117="","",V117-AC117)</f>
+      </c>
+    </row>
+    <row r="118" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="J118" s="3"/>
@@ -6172,16 +6196,16 @@
         <f>IF($K118="","",L118-M118-N118-O118-P118-Q118-R118-S118-T118)</f>
       </c>
       <c r="W118" s="3">
-        <f>IF($K118="","",(V118-Y118)/J118*100)</f>
+        <f>IF($K118="","",(V118-AC118)/J118*100)</f>
       </c>
       <c r="X118" s="3">
         <f>IF($K118="","",M118-U118)</f>
       </c>
-      <c r="Z118" s="3">
-        <f>IF($K118="","",V118-Y118)</f>
-      </c>
-    </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD118" s="3">
+        <f>IF($K118="","",V118-AC118)</f>
+      </c>
+    </row>
+    <row r="119" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="J119" s="3"/>
@@ -6218,16 +6242,16 @@
         <f>IF($K119="","",L119-M119-N119-O119-P119-Q119-R119-S119-T119)</f>
       </c>
       <c r="W119" s="3">
-        <f>IF($K119="","",(V119-Y119)/J119*100)</f>
+        <f>IF($K119="","",(V119-AC119)/J119*100)</f>
       </c>
       <c r="X119" s="3">
         <f>IF($K119="","",M119-U119)</f>
       </c>
-      <c r="Z119" s="3">
-        <f>IF($K119="","",V119-Y119)</f>
-      </c>
-    </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD119" s="3">
+        <f>IF($K119="","",V119-AC119)</f>
+      </c>
+    </row>
+    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="J120" s="3"/>
@@ -6264,16 +6288,16 @@
         <f>IF($K120="","",L120-M120-N120-O120-P120-Q120-R120-S120-T120)</f>
       </c>
       <c r="W120" s="3">
-        <f>IF($K120="","",(V120-Y120)/J120*100)</f>
+        <f>IF($K120="","",(V120-AC120)/J120*100)</f>
       </c>
       <c r="X120" s="3">
         <f>IF($K120="","",M120-U120)</f>
       </c>
-      <c r="Z120" s="3">
-        <f>IF($K120="","",V120-Y120)</f>
-      </c>
-    </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD120" s="3">
+        <f>IF($K120="","",V120-AC120)</f>
+      </c>
+    </row>
+    <row r="121" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="J121" s="3"/>
@@ -6310,16 +6334,16 @@
         <f>IF($K121="","",L121-M121-N121-O121-P121-Q121-R121-S121-T121)</f>
       </c>
       <c r="W121" s="3">
-        <f>IF($K121="","",(V121-Y121)/J121*100)</f>
+        <f>IF($K121="","",(V121-AC121)/J121*100)</f>
       </c>
       <c r="X121" s="3">
         <f>IF($K121="","",M121-U121)</f>
       </c>
-      <c r="Z121" s="3">
-        <f>IF($K121="","",V121-Y121)</f>
-      </c>
-    </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD121" s="3">
+        <f>IF($K121="","",V121-AC121)</f>
+      </c>
+    </row>
+    <row r="122" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="J122" s="3"/>
@@ -6356,16 +6380,16 @@
         <f>IF($K122="","",L122-M122-N122-O122-P122-Q122-R122-S122-T122)</f>
       </c>
       <c r="W122" s="3">
-        <f>IF($K122="","",(V122-Y122)/J122*100)</f>
+        <f>IF($K122="","",(V122-AC122)/J122*100)</f>
       </c>
       <c r="X122" s="3">
         <f>IF($K122="","",M122-U122)</f>
       </c>
-      <c r="Z122" s="3">
-        <f>IF($K122="","",V122-Y122)</f>
-      </c>
-    </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD122" s="3">
+        <f>IF($K122="","",V122-AC122)</f>
+      </c>
+    </row>
+    <row r="123" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="J123" s="3"/>
@@ -6402,16 +6426,16 @@
         <f>IF($K123="","",L123-M123-N123-O123-P123-Q123-R123-S123-T123)</f>
       </c>
       <c r="W123" s="3">
-        <f>IF($K123="","",(V123-Y123)/J123*100)</f>
+        <f>IF($K123="","",(V123-AC123)/J123*100)</f>
       </c>
       <c r="X123" s="3">
         <f>IF($K123="","",M123-U123)</f>
       </c>
-      <c r="Z123" s="3">
-        <f>IF($K123="","",V123-Y123)</f>
-      </c>
-    </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD123" s="3">
+        <f>IF($K123="","",V123-AC123)</f>
+      </c>
+    </row>
+    <row r="124" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="J124" s="3"/>
@@ -6448,16 +6472,16 @@
         <f>IF($K124="","",L124-M124-N124-O124-P124-Q124-R124-S124-T124)</f>
       </c>
       <c r="W124" s="3">
-        <f>IF($K124="","",(V124-Y124)/J124*100)</f>
+        <f>IF($K124="","",(V124-AC124)/J124*100)</f>
       </c>
       <c r="X124" s="3">
         <f>IF($K124="","",M124-U124)</f>
       </c>
-      <c r="Z124" s="3">
-        <f>IF($K124="","",V124-Y124)</f>
-      </c>
-    </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD124" s="3">
+        <f>IF($K124="","",V124-AC124)</f>
+      </c>
+    </row>
+    <row r="125" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="J125" s="3"/>
@@ -6494,16 +6518,16 @@
         <f>IF($K125="","",L125-M125-N125-O125-P125-Q125-R125-S125-T125)</f>
       </c>
       <c r="W125" s="3">
-        <f>IF($K125="","",(V125-Y125)/J125*100)</f>
+        <f>IF($K125="","",(V125-AC125)/J125*100)</f>
       </c>
       <c r="X125" s="3">
         <f>IF($K125="","",M125-U125)</f>
       </c>
-      <c r="Z125" s="3">
-        <f>IF($K125="","",V125-Y125)</f>
-      </c>
-    </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD125" s="3">
+        <f>IF($K125="","",V125-AC125)</f>
+      </c>
+    </row>
+    <row r="126" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="J126" s="3"/>
@@ -6540,16 +6564,16 @@
         <f>IF($K126="","",L126-M126-N126-O126-P126-Q126-R126-S126-T126)</f>
       </c>
       <c r="W126" s="3">
-        <f>IF($K126="","",(V126-Y126)/J126*100)</f>
+        <f>IF($K126="","",(V126-AC126)/J126*100)</f>
       </c>
       <c r="X126" s="3">
         <f>IF($K126="","",M126-U126)</f>
       </c>
-      <c r="Z126" s="3">
-        <f>IF($K126="","",V126-Y126)</f>
-      </c>
-    </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD126" s="3">
+        <f>IF($K126="","",V126-AC126)</f>
+      </c>
+    </row>
+    <row r="127" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="J127" s="3"/>
@@ -6586,16 +6610,16 @@
         <f>IF($K127="","",L127-M127-N127-O127-P127-Q127-R127-S127-T127)</f>
       </c>
       <c r="W127" s="3">
-        <f>IF($K127="","",(V127-Y127)/J127*100)</f>
+        <f>IF($K127="","",(V127-AC127)/J127*100)</f>
       </c>
       <c r="X127" s="3">
         <f>IF($K127="","",M127-U127)</f>
       </c>
-      <c r="Z127" s="3">
-        <f>IF($K127="","",V127-Y127)</f>
-      </c>
-    </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD127" s="3">
+        <f>IF($K127="","",V127-AC127)</f>
+      </c>
+    </row>
+    <row r="128" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="J128" s="3"/>
@@ -6632,16 +6656,16 @@
         <f>IF($K128="","",L128-M128-N128-O128-P128-Q128-R128-S128-T128)</f>
       </c>
       <c r="W128" s="3">
-        <f>IF($K128="","",(V128-Y128)/J128*100)</f>
+        <f>IF($K128="","",(V128-AC128)/J128*100)</f>
       </c>
       <c r="X128" s="3">
         <f>IF($K128="","",M128-U128)</f>
       </c>
-      <c r="Z128" s="3">
-        <f>IF($K128="","",V128-Y128)</f>
-      </c>
-    </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD128" s="3">
+        <f>IF($K128="","",V128-AC128)</f>
+      </c>
+    </row>
+    <row r="129" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="J129" s="3"/>
@@ -6678,16 +6702,16 @@
         <f>IF($K129="","",L129-M129-N129-O129-P129-Q129-R129-S129-T129)</f>
       </c>
       <c r="W129" s="3">
-        <f>IF($K129="","",(V129-Y129)/J129*100)</f>
+        <f>IF($K129="","",(V129-AC129)/J129*100)</f>
       </c>
       <c r="X129" s="3">
         <f>IF($K129="","",M129-U129)</f>
       </c>
-      <c r="Z129" s="3">
-        <f>IF($K129="","",V129-Y129)</f>
-      </c>
-    </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD129" s="3">
+        <f>IF($K129="","",V129-AC129)</f>
+      </c>
+    </row>
+    <row r="130" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="J130" s="3"/>
@@ -6724,16 +6748,16 @@
         <f>IF($K130="","",L130-M130-N130-O130-P130-Q130-R130-S130-T130)</f>
       </c>
       <c r="W130" s="3">
-        <f>IF($K130="","",(V130-Y130)/J130*100)</f>
+        <f>IF($K130="","",(V130-AC130)/J130*100)</f>
       </c>
       <c r="X130" s="3">
         <f>IF($K130="","",M130-U130)</f>
       </c>
-      <c r="Z130" s="3">
-        <f>IF($K130="","",V130-Y130)</f>
-      </c>
-    </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD130" s="3">
+        <f>IF($K130="","",V130-AC130)</f>
+      </c>
+    </row>
+    <row r="131" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="J131" s="3"/>
@@ -6770,16 +6794,16 @@
         <f>IF($K131="","",L131-M131-N131-O131-P131-Q131-R131-S131-T131)</f>
       </c>
       <c r="W131" s="3">
-        <f>IF($K131="","",(V131-Y131)/J131*100)</f>
+        <f>IF($K131="","",(V131-AC131)/J131*100)</f>
       </c>
       <c r="X131" s="3">
         <f>IF($K131="","",M131-U131)</f>
       </c>
-      <c r="Z131" s="3">
-        <f>IF($K131="","",V131-Y131)</f>
-      </c>
-    </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD131" s="3">
+        <f>IF($K131="","",V131-AC131)</f>
+      </c>
+    </row>
+    <row r="132" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="J132" s="3"/>
@@ -6816,16 +6840,16 @@
         <f>IF($K132="","",L132-M132-N132-O132-P132-Q132-R132-S132-T132)</f>
       </c>
       <c r="W132" s="3">
-        <f>IF($K132="","",(V132-Y132)/J132*100)</f>
+        <f>IF($K132="","",(V132-AC132)/J132*100)</f>
       </c>
       <c r="X132" s="3">
         <f>IF($K132="","",M132-U132)</f>
       </c>
-      <c r="Z132" s="3">
-        <f>IF($K132="","",V132-Y132)</f>
-      </c>
-    </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD132" s="3">
+        <f>IF($K132="","",V132-AC132)</f>
+      </c>
+    </row>
+    <row r="133" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="J133" s="3"/>
@@ -6862,16 +6886,16 @@
         <f>IF($K133="","",L133-M133-N133-O133-P133-Q133-R133-S133-T133)</f>
       </c>
       <c r="W133" s="3">
-        <f>IF($K133="","",(V133-Y133)/J133*100)</f>
+        <f>IF($K133="","",(V133-AC133)/J133*100)</f>
       </c>
       <c r="X133" s="3">
         <f>IF($K133="","",M133-U133)</f>
       </c>
-      <c r="Z133" s="3">
-        <f>IF($K133="","",V133-Y133)</f>
-      </c>
-    </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD133" s="3">
+        <f>IF($K133="","",V133-AC133)</f>
+      </c>
+    </row>
+    <row r="134" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="J134" s="3"/>
@@ -6908,16 +6932,16 @@
         <f>IF($K134="","",L134-M134-N134-O134-P134-Q134-R134-S134-T134)</f>
       </c>
       <c r="W134" s="3">
-        <f>IF($K134="","",(V134-Y134)/J134*100)</f>
+        <f>IF($K134="","",(V134-AC134)/J134*100)</f>
       </c>
       <c r="X134" s="3">
         <f>IF($K134="","",M134-U134)</f>
       </c>
-      <c r="Z134" s="3">
-        <f>IF($K134="","",V134-Y134)</f>
-      </c>
-    </row>
-    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD134" s="3">
+        <f>IF($K134="","",V134-AC134)</f>
+      </c>
+    </row>
+    <row r="135" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="J135" s="3"/>
@@ -6954,16 +6978,16 @@
         <f>IF($K135="","",L135-M135-N135-O135-P135-Q135-R135-S135-T135)</f>
       </c>
       <c r="W135" s="3">
-        <f>IF($K135="","",(V135-Y135)/J135*100)</f>
+        <f>IF($K135="","",(V135-AC135)/J135*100)</f>
       </c>
       <c r="X135" s="3">
         <f>IF($K135="","",M135-U135)</f>
       </c>
-      <c r="Z135" s="3">
-        <f>IF($K135="","",V135-Y135)</f>
-      </c>
-    </row>
-    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD135" s="3">
+        <f>IF($K135="","",V135-AC135)</f>
+      </c>
+    </row>
+    <row r="136" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="J136" s="3"/>
@@ -7000,16 +7024,16 @@
         <f>IF($K136="","",L136-M136-N136-O136-P136-Q136-R136-S136-T136)</f>
       </c>
       <c r="W136" s="3">
-        <f>IF($K136="","",(V136-Y136)/J136*100)</f>
+        <f>IF($K136="","",(V136-AC136)/J136*100)</f>
       </c>
       <c r="X136" s="3">
         <f>IF($K136="","",M136-U136)</f>
       </c>
-      <c r="Z136" s="3">
-        <f>IF($K136="","",V136-Y136)</f>
-      </c>
-    </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD136" s="3">
+        <f>IF($K136="","",V136-AC136)</f>
+      </c>
+    </row>
+    <row r="137" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="J137" s="3"/>
@@ -7046,16 +7070,16 @@
         <f>IF($K137="","",L137-M137-N137-O137-P137-Q137-R137-S137-T137)</f>
       </c>
       <c r="W137" s="3">
-        <f>IF($K137="","",(V137-Y137)/J137*100)</f>
+        <f>IF($K137="","",(V137-AC137)/J137*100)</f>
       </c>
       <c r="X137" s="3">
         <f>IF($K137="","",M137-U137)</f>
       </c>
-      <c r="Z137" s="3">
-        <f>IF($K137="","",V137-Y137)</f>
-      </c>
-    </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD137" s="3">
+        <f>IF($K137="","",V137-AC137)</f>
+      </c>
+    </row>
+    <row r="138" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="J138" s="3"/>
@@ -7092,16 +7116,16 @@
         <f>IF($K138="","",L138-M138-N138-O138-P138-Q138-R138-S138-T138)</f>
       </c>
       <c r="W138" s="3">
-        <f>IF($K138="","",(V138-Y138)/J138*100)</f>
+        <f>IF($K138="","",(V138-AC138)/J138*100)</f>
       </c>
       <c r="X138" s="3">
         <f>IF($K138="","",M138-U138)</f>
       </c>
-      <c r="Z138" s="3">
-        <f>IF($K138="","",V138-Y138)</f>
-      </c>
-    </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD138" s="3">
+        <f>IF($K138="","",V138-AC138)</f>
+      </c>
+    </row>
+    <row r="139" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="J139" s="3"/>
@@ -7138,16 +7162,16 @@
         <f>IF($K139="","",L139-M139-N139-O139-P139-Q139-R139-S139-T139)</f>
       </c>
       <c r="W139" s="3">
-        <f>IF($K139="","",(V139-Y139)/J139*100)</f>
+        <f>IF($K139="","",(V139-AC139)/J139*100)</f>
       </c>
       <c r="X139" s="3">
         <f>IF($K139="","",M139-U139)</f>
       </c>
-      <c r="Z139" s="3">
-        <f>IF($K139="","",V139-Y139)</f>
-      </c>
-    </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD139" s="3">
+        <f>IF($K139="","",V139-AC139)</f>
+      </c>
+    </row>
+    <row r="140" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="J140" s="3"/>
@@ -7184,16 +7208,16 @@
         <f>IF($K140="","",L140-M140-N140-O140-P140-Q140-R140-S140-T140)</f>
       </c>
       <c r="W140" s="3">
-        <f>IF($K140="","",(V140-Y140)/J140*100)</f>
+        <f>IF($K140="","",(V140-AC140)/J140*100)</f>
       </c>
       <c r="X140" s="3">
         <f>IF($K140="","",M140-U140)</f>
       </c>
-      <c r="Z140" s="3">
-        <f>IF($K140="","",V140-Y140)</f>
-      </c>
-    </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD140" s="3">
+        <f>IF($K140="","",V140-AC140)</f>
+      </c>
+    </row>
+    <row r="141" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="J141" s="3"/>
@@ -7230,16 +7254,16 @@
         <f>IF($K141="","",L141-M141-N141-O141-P141-Q141-R141-S141-T141)</f>
       </c>
       <c r="W141" s="3">
-        <f>IF($K141="","",(V141-Y141)/J141*100)</f>
+        <f>IF($K141="","",(V141-AC141)/J141*100)</f>
       </c>
       <c r="X141" s="3">
         <f>IF($K141="","",M141-U141)</f>
       </c>
-      <c r="Z141" s="3">
-        <f>IF($K141="","",V141-Y141)</f>
-      </c>
-    </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD141" s="3">
+        <f>IF($K141="","",V141-AC141)</f>
+      </c>
+    </row>
+    <row r="142" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="J142" s="3"/>
@@ -7276,16 +7300,16 @@
         <f>IF($K142="","",L142-M142-N142-O142-P142-Q142-R142-S142-T142)</f>
       </c>
       <c r="W142" s="3">
-        <f>IF($K142="","",(V142-Y142)/J142*100)</f>
+        <f>IF($K142="","",(V142-AC142)/J142*100)</f>
       </c>
       <c r="X142" s="3">
         <f>IF($K142="","",M142-U142)</f>
       </c>
-      <c r="Z142" s="3">
-        <f>IF($K142="","",V142-Y142)</f>
-      </c>
-    </row>
-    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD142" s="3">
+        <f>IF($K142="","",V142-AC142)</f>
+      </c>
+    </row>
+    <row r="143" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="J143" s="3"/>
@@ -7322,16 +7346,16 @@
         <f>IF($K143="","",L143-M143-N143-O143-P143-Q143-R143-S143-T143)</f>
       </c>
       <c r="W143" s="3">
-        <f>IF($K143="","",(V143-Y143)/J143*100)</f>
+        <f>IF($K143="","",(V143-AC143)/J143*100)</f>
       </c>
       <c r="X143" s="3">
         <f>IF($K143="","",M143-U143)</f>
       </c>
-      <c r="Z143" s="3">
-        <f>IF($K143="","",V143-Y143)</f>
-      </c>
-    </row>
-    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD143" s="3">
+        <f>IF($K143="","",V143-AC143)</f>
+      </c>
+    </row>
+    <row r="144" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="J144" s="3"/>
@@ -7368,16 +7392,16 @@
         <f>IF($K144="","",L144-M144-N144-O144-P144-Q144-R144-S144-T144)</f>
       </c>
       <c r="W144" s="3">
-        <f>IF($K144="","",(V144-Y144)/J144*100)</f>
+        <f>IF($K144="","",(V144-AC144)/J144*100)</f>
       </c>
       <c r="X144" s="3">
         <f>IF($K144="","",M144-U144)</f>
       </c>
-      <c r="Z144" s="3">
-        <f>IF($K144="","",V144-Y144)</f>
-      </c>
-    </row>
-    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD144" s="3">
+        <f>IF($K144="","",V144-AC144)</f>
+      </c>
+    </row>
+    <row r="145" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="J145" s="3"/>
@@ -7414,16 +7438,16 @@
         <f>IF($K145="","",L145-M145-N145-O145-P145-Q145-R145-S145-T145)</f>
       </c>
       <c r="W145" s="3">
-        <f>IF($K145="","",(V145-Y145)/J145*100)</f>
+        <f>IF($K145="","",(V145-AC145)/J145*100)</f>
       </c>
       <c r="X145" s="3">
         <f>IF($K145="","",M145-U145)</f>
       </c>
-      <c r="Z145" s="3">
-        <f>IF($K145="","",V145-Y145)</f>
-      </c>
-    </row>
-    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD145" s="3">
+        <f>IF($K145="","",V145-AC145)</f>
+      </c>
+    </row>
+    <row r="146" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="J146" s="3"/>
@@ -7460,16 +7484,16 @@
         <f>IF($K146="","",L146-M146-N146-O146-P146-Q146-R146-S146-T146)</f>
       </c>
       <c r="W146" s="3">
-        <f>IF($K146="","",(V146-Y146)/J146*100)</f>
+        <f>IF($K146="","",(V146-AC146)/J146*100)</f>
       </c>
       <c r="X146" s="3">
         <f>IF($K146="","",M146-U146)</f>
       </c>
-      <c r="Z146" s="3">
-        <f>IF($K146="","",V146-Y146)</f>
-      </c>
-    </row>
-    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD146" s="3">
+        <f>IF($K146="","",V146-AC146)</f>
+      </c>
+    </row>
+    <row r="147" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="J147" s="3"/>
@@ -7506,16 +7530,16 @@
         <f>IF($K147="","",L147-M147-N147-O147-P147-Q147-R147-S147-T147)</f>
       </c>
       <c r="W147" s="3">
-        <f>IF($K147="","",(V147-Y147)/J147*100)</f>
+        <f>IF($K147="","",(V147-AC147)/J147*100)</f>
       </c>
       <c r="X147" s="3">
         <f>IF($K147="","",M147-U147)</f>
       </c>
-      <c r="Z147" s="3">
-        <f>IF($K147="","",V147-Y147)</f>
-      </c>
-    </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD147" s="3">
+        <f>IF($K147="","",V147-AC147)</f>
+      </c>
+    </row>
+    <row r="148" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="J148" s="3"/>
@@ -7552,16 +7576,16 @@
         <f>IF($K148="","",L148-M148-N148-O148-P148-Q148-R148-S148-T148)</f>
       </c>
       <c r="W148" s="3">
-        <f>IF($K148="","",(V148-Y148)/J148*100)</f>
+        <f>IF($K148="","",(V148-AC148)/J148*100)</f>
       </c>
       <c r="X148" s="3">
         <f>IF($K148="","",M148-U148)</f>
       </c>
-      <c r="Z148" s="3">
-        <f>IF($K148="","",V148-Y148)</f>
-      </c>
-    </row>
-    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD148" s="3">
+        <f>IF($K148="","",V148-AC148)</f>
+      </c>
+    </row>
+    <row r="149" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="J149" s="3"/>
@@ -7598,16 +7622,16 @@
         <f>IF($K149="","",L149-M149-N149-O149-P149-Q149-R149-S149-T149)</f>
       </c>
       <c r="W149" s="3">
-        <f>IF($K149="","",(V149-Y149)/J149*100)</f>
+        <f>IF($K149="","",(V149-AC149)/J149*100)</f>
       </c>
       <c r="X149" s="3">
         <f>IF($K149="","",M149-U149)</f>
       </c>
-      <c r="Z149" s="3">
-        <f>IF($K149="","",V149-Y149)</f>
-      </c>
-    </row>
-    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD149" s="3">
+        <f>IF($K149="","",V149-AC149)</f>
+      </c>
+    </row>
+    <row r="150" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="J150" s="3"/>
@@ -7644,16 +7668,16 @@
         <f>IF($K150="","",L150-M150-N150-O150-P150-Q150-R150-S150-T150)</f>
       </c>
       <c r="W150" s="3">
-        <f>IF($K150="","",(V150-Y150)/J150*100)</f>
+        <f>IF($K150="","",(V150-AC150)/J150*100)</f>
       </c>
       <c r="X150" s="3">
         <f>IF($K150="","",M150-U150)</f>
       </c>
-      <c r="Z150" s="3">
-        <f>IF($K150="","",V150-Y150)</f>
-      </c>
-    </row>
-    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD150" s="3">
+        <f>IF($K150="","",V150-AC150)</f>
+      </c>
+    </row>
+    <row r="151" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="J151" s="3"/>
@@ -7690,16 +7714,16 @@
         <f>IF($K151="","",L151-M151-N151-O151-P151-Q151-R151-S151-T151)</f>
       </c>
       <c r="W151" s="3">
-        <f>IF($K151="","",(V151-Y151)/J151*100)</f>
+        <f>IF($K151="","",(V151-AC151)/J151*100)</f>
       </c>
       <c r="X151" s="3">
         <f>IF($K151="","",M151-U151)</f>
       </c>
-      <c r="Z151" s="3">
-        <f>IF($K151="","",V151-Y151)</f>
-      </c>
-    </row>
-    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD151" s="3">
+        <f>IF($K151="","",V151-AC151)</f>
+      </c>
+    </row>
+    <row r="152" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="J152" s="3"/>
@@ -7736,16 +7760,16 @@
         <f>IF($K152="","",L152-M152-N152-O152-P152-Q152-R152-S152-T152)</f>
       </c>
       <c r="W152" s="3">
-        <f>IF($K152="","",(V152-Y152)/J152*100)</f>
+        <f>IF($K152="","",(V152-AC152)/J152*100)</f>
       </c>
       <c r="X152" s="3">
         <f>IF($K152="","",M152-U152)</f>
       </c>
-      <c r="Z152" s="3">
-        <f>IF($K152="","",V152-Y152)</f>
-      </c>
-    </row>
-    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD152" s="3">
+        <f>IF($K152="","",V152-AC152)</f>
+      </c>
+    </row>
+    <row r="153" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="J153" s="3"/>
@@ -7782,16 +7806,16 @@
         <f>IF($K153="","",L153-M153-N153-O153-P153-Q153-R153-S153-T153)</f>
       </c>
       <c r="W153" s="3">
-        <f>IF($K153="","",(V153-Y153)/J153*100)</f>
+        <f>IF($K153="","",(V153-AC153)/J153*100)</f>
       </c>
       <c r="X153" s="3">
         <f>IF($K153="","",M153-U153)</f>
       </c>
-      <c r="Z153" s="3">
-        <f>IF($K153="","",V153-Y153)</f>
-      </c>
-    </row>
-    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD153" s="3">
+        <f>IF($K153="","",V153-AC153)</f>
+      </c>
+    </row>
+    <row r="154" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="J154" s="3"/>
@@ -7828,16 +7852,16 @@
         <f>IF($K154="","",L154-M154-N154-O154-P154-Q154-R154-S154-T154)</f>
       </c>
       <c r="W154" s="3">
-        <f>IF($K154="","",(V154-Y154)/J154*100)</f>
+        <f>IF($K154="","",(V154-AC154)/J154*100)</f>
       </c>
       <c r="X154" s="3">
         <f>IF($K154="","",M154-U154)</f>
       </c>
-      <c r="Z154" s="3">
-        <f>IF($K154="","",V154-Y154)</f>
-      </c>
-    </row>
-    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD154" s="3">
+        <f>IF($K154="","",V154-AC154)</f>
+      </c>
+    </row>
+    <row r="155" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="J155" s="3"/>
@@ -7874,16 +7898,16 @@
         <f>IF($K155="","",L155-M155-N155-O155-P155-Q155-R155-S155-T155)</f>
       </c>
       <c r="W155" s="3">
-        <f>IF($K155="","",(V155-Y155)/J155*100)</f>
+        <f>IF($K155="","",(V155-AC155)/J155*100)</f>
       </c>
       <c r="X155" s="3">
         <f>IF($K155="","",M155-U155)</f>
       </c>
-      <c r="Z155" s="3">
-        <f>IF($K155="","",V155-Y155)</f>
-      </c>
-    </row>
-    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD155" s="3">
+        <f>IF($K155="","",V155-AC155)</f>
+      </c>
+    </row>
+    <row r="156" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="J156" s="3"/>
@@ -7920,16 +7944,16 @@
         <f>IF($K156="","",L156-M156-N156-O156-P156-Q156-R156-S156-T156)</f>
       </c>
       <c r="W156" s="3">
-        <f>IF($K156="","",(V156-Y156)/J156*100)</f>
+        <f>IF($K156="","",(V156-AC156)/J156*100)</f>
       </c>
       <c r="X156" s="3">
         <f>IF($K156="","",M156-U156)</f>
       </c>
-      <c r="Z156" s="3">
-        <f>IF($K156="","",V156-Y156)</f>
-      </c>
-    </row>
-    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD156" s="3">
+        <f>IF($K156="","",V156-AC156)</f>
+      </c>
+    </row>
+    <row r="157" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="J157" s="3"/>
@@ -7966,16 +7990,16 @@
         <f>IF($K157="","",L157-M157-N157-O157-P157-Q157-R157-S157-T157)</f>
       </c>
       <c r="W157" s="3">
-        <f>IF($K157="","",(V157-Y157)/J157*100)</f>
+        <f>IF($K157="","",(V157-AC157)/J157*100)</f>
       </c>
       <c r="X157" s="3">
         <f>IF($K157="","",M157-U157)</f>
       </c>
-      <c r="Z157" s="3">
-        <f>IF($K157="","",V157-Y157)</f>
-      </c>
-    </row>
-    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD157" s="3">
+        <f>IF($K157="","",V157-AC157)</f>
+      </c>
+    </row>
+    <row r="158" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="J158" s="3"/>
@@ -8012,16 +8036,16 @@
         <f>IF($K158="","",L158-M158-N158-O158-P158-Q158-R158-S158-T158)</f>
       </c>
       <c r="W158" s="3">
-        <f>IF($K158="","",(V158-Y158)/J158*100)</f>
+        <f>IF($K158="","",(V158-AC158)/J158*100)</f>
       </c>
       <c r="X158" s="3">
         <f>IF($K158="","",M158-U158)</f>
       </c>
-      <c r="Z158" s="3">
-        <f>IF($K158="","",V158-Y158)</f>
-      </c>
-    </row>
-    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD158" s="3">
+        <f>IF($K158="","",V158-AC158)</f>
+      </c>
+    </row>
+    <row r="159" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="J159" s="3"/>
@@ -8058,16 +8082,16 @@
         <f>IF($K159="","",L159-M159-N159-O159-P159-Q159-R159-S159-T159)</f>
       </c>
       <c r="W159" s="3">
-        <f>IF($K159="","",(V159-Y159)/J159*100)</f>
+        <f>IF($K159="","",(V159-AC159)/J159*100)</f>
       </c>
       <c r="X159" s="3">
         <f>IF($K159="","",M159-U159)</f>
       </c>
-      <c r="Z159" s="3">
-        <f>IF($K159="","",V159-Y159)</f>
-      </c>
-    </row>
-    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD159" s="3">
+        <f>IF($K159="","",V159-AC159)</f>
+      </c>
+    </row>
+    <row r="160" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="J160" s="3"/>
@@ -8104,16 +8128,16 @@
         <f>IF($K160="","",L160-M160-N160-O160-P160-Q160-R160-S160-T160)</f>
       </c>
       <c r="W160" s="3">
-        <f>IF($K160="","",(V160-Y160)/J160*100)</f>
+        <f>IF($K160="","",(V160-AC160)/J160*100)</f>
       </c>
       <c r="X160" s="3">
         <f>IF($K160="","",M160-U160)</f>
       </c>
-      <c r="Z160" s="3">
-        <f>IF($K160="","",V160-Y160)</f>
-      </c>
-    </row>
-    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD160" s="3">
+        <f>IF($K160="","",V160-AC160)</f>
+      </c>
+    </row>
+    <row r="161" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="J161" s="3"/>
@@ -8150,16 +8174,16 @@
         <f>IF($K161="","",L161-M161-N161-O161-P161-Q161-R161-S161-T161)</f>
       </c>
       <c r="W161" s="3">
-        <f>IF($K161="","",(V161-Y161)/J161*100)</f>
+        <f>IF($K161="","",(V161-AC161)/J161*100)</f>
       </c>
       <c r="X161" s="3">
         <f>IF($K161="","",M161-U161)</f>
       </c>
-      <c r="Z161" s="3">
-        <f>IF($K161="","",V161-Y161)</f>
-      </c>
-    </row>
-    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD161" s="3">
+        <f>IF($K161="","",V161-AC161)</f>
+      </c>
+    </row>
+    <row r="162" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="J162" s="3"/>
@@ -8196,16 +8220,16 @@
         <f>IF($K162="","",L162-M162-N162-O162-P162-Q162-R162-S162-T162)</f>
       </c>
       <c r="W162" s="3">
-        <f>IF($K162="","",(V162-Y162)/J162*100)</f>
+        <f>IF($K162="","",(V162-AC162)/J162*100)</f>
       </c>
       <c r="X162" s="3">
         <f>IF($K162="","",M162-U162)</f>
       </c>
-      <c r="Z162" s="3">
-        <f>IF($K162="","",V162-Y162)</f>
-      </c>
-    </row>
-    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD162" s="3">
+        <f>IF($K162="","",V162-AC162)</f>
+      </c>
+    </row>
+    <row r="163" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="J163" s="3"/>
@@ -8242,16 +8266,16 @@
         <f>IF($K163="","",L163-M163-N163-O163-P163-Q163-R163-S163-T163)</f>
       </c>
       <c r="W163" s="3">
-        <f>IF($K163="","",(V163-Y163)/J163*100)</f>
+        <f>IF($K163="","",(V163-AC163)/J163*100)</f>
       </c>
       <c r="X163" s="3">
         <f>IF($K163="","",M163-U163)</f>
       </c>
-      <c r="Z163" s="3">
-        <f>IF($K163="","",V163-Y163)</f>
-      </c>
-    </row>
-    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD163" s="3">
+        <f>IF($K163="","",V163-AC163)</f>
+      </c>
+    </row>
+    <row r="164" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="J164" s="3"/>
@@ -8288,16 +8312,16 @@
         <f>IF($K164="","",L164-M164-N164-O164-P164-Q164-R164-S164-T164)</f>
       </c>
       <c r="W164" s="3">
-        <f>IF($K164="","",(V164-Y164)/J164*100)</f>
+        <f>IF($K164="","",(V164-AC164)/J164*100)</f>
       </c>
       <c r="X164" s="3">
         <f>IF($K164="","",M164-U164)</f>
       </c>
-      <c r="Z164" s="3">
-        <f>IF($K164="","",V164-Y164)</f>
-      </c>
-    </row>
-    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD164" s="3">
+        <f>IF($K164="","",V164-AC164)</f>
+      </c>
+    </row>
+    <row r="165" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="J165" s="3"/>
@@ -8334,16 +8358,16 @@
         <f>IF($K165="","",L165-M165-N165-O165-P165-Q165-R165-S165-T165)</f>
       </c>
       <c r="W165" s="3">
-        <f>IF($K165="","",(V165-Y165)/J165*100)</f>
+        <f>IF($K165="","",(V165-AC165)/J165*100)</f>
       </c>
       <c r="X165" s="3">
         <f>IF($K165="","",M165-U165)</f>
       </c>
-      <c r="Z165" s="3">
-        <f>IF($K165="","",V165-Y165)</f>
-      </c>
-    </row>
-    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD165" s="3">
+        <f>IF($K165="","",V165-AC165)</f>
+      </c>
+    </row>
+    <row r="166" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="J166" s="3"/>
@@ -8380,16 +8404,16 @@
         <f>IF($K166="","",L166-M166-N166-O166-P166-Q166-R166-S166-T166)</f>
       </c>
       <c r="W166" s="3">
-        <f>IF($K166="","",(V166-Y166)/J166*100)</f>
+        <f>IF($K166="","",(V166-AC166)/J166*100)</f>
       </c>
       <c r="X166" s="3">
         <f>IF($K166="","",M166-U166)</f>
       </c>
-      <c r="Z166" s="3">
-        <f>IF($K166="","",V166-Y166)</f>
-      </c>
-    </row>
-    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD166" s="3">
+        <f>IF($K166="","",V166-AC166)</f>
+      </c>
+    </row>
+    <row r="167" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="J167" s="3"/>
@@ -8426,16 +8450,16 @@
         <f>IF($K167="","",L167-M167-N167-O167-P167-Q167-R167-S167-T167)</f>
       </c>
       <c r="W167" s="3">
-        <f>IF($K167="","",(V167-Y167)/J167*100)</f>
+        <f>IF($K167="","",(V167-AC167)/J167*100)</f>
       </c>
       <c r="X167" s="3">
         <f>IF($K167="","",M167-U167)</f>
       </c>
-      <c r="Z167" s="3">
-        <f>IF($K167="","",V167-Y167)</f>
-      </c>
-    </row>
-    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD167" s="3">
+        <f>IF($K167="","",V167-AC167)</f>
+      </c>
+    </row>
+    <row r="168" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="J168" s="3"/>
@@ -8472,16 +8496,16 @@
         <f>IF($K168="","",L168-M168-N168-O168-P168-Q168-R168-S168-T168)</f>
       </c>
       <c r="W168" s="3">
-        <f>IF($K168="","",(V168-Y168)/J168*100)</f>
+        <f>IF($K168="","",(V168-AC168)/J168*100)</f>
       </c>
       <c r="X168" s="3">
         <f>IF($K168="","",M168-U168)</f>
       </c>
-      <c r="Z168" s="3">
-        <f>IF($K168="","",V168-Y168)</f>
-      </c>
-    </row>
-    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD168" s="3">
+        <f>IF($K168="","",V168-AC168)</f>
+      </c>
+    </row>
+    <row r="169" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="J169" s="3"/>
@@ -8518,16 +8542,16 @@
         <f>IF($K169="","",L169-M169-N169-O169-P169-Q169-R169-S169-T169)</f>
       </c>
       <c r="W169" s="3">
-        <f>IF($K169="","",(V169-Y169)/J169*100)</f>
+        <f>IF($K169="","",(V169-AC169)/J169*100)</f>
       </c>
       <c r="X169" s="3">
         <f>IF($K169="","",M169-U169)</f>
       </c>
-      <c r="Z169" s="3">
-        <f>IF($K169="","",V169-Y169)</f>
-      </c>
-    </row>
-    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD169" s="3">
+        <f>IF($K169="","",V169-AC169)</f>
+      </c>
+    </row>
+    <row r="170" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="J170" s="3"/>
@@ -8564,16 +8588,16 @@
         <f>IF($K170="","",L170-M170-N170-O170-P170-Q170-R170-S170-T170)</f>
       </c>
       <c r="W170" s="3">
-        <f>IF($K170="","",(V170-Y170)/J170*100)</f>
+        <f>IF($K170="","",(V170-AC170)/J170*100)</f>
       </c>
       <c r="X170" s="3">
         <f>IF($K170="","",M170-U170)</f>
       </c>
-      <c r="Z170" s="3">
-        <f>IF($K170="","",V170-Y170)</f>
-      </c>
-    </row>
-    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD170" s="3">
+        <f>IF($K170="","",V170-AC170)</f>
+      </c>
+    </row>
+    <row r="171" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="J171" s="3"/>
@@ -8610,16 +8634,16 @@
         <f>IF($K171="","",L171-M171-N171-O171-P171-Q171-R171-S171-T171)</f>
       </c>
       <c r="W171" s="3">
-        <f>IF($K171="","",(V171-Y171)/J171*100)</f>
+        <f>IF($K171="","",(V171-AC171)/J171*100)</f>
       </c>
       <c r="X171" s="3">
         <f>IF($K171="","",M171-U171)</f>
       </c>
-      <c r="Z171" s="3">
-        <f>IF($K171="","",V171-Y171)</f>
-      </c>
-    </row>
-    <row r="172" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD171" s="3">
+        <f>IF($K171="","",V171-AC171)</f>
+      </c>
+    </row>
+    <row r="172" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="J172" s="3"/>
@@ -8656,16 +8680,16 @@
         <f>IF($K172="","",L172-M172-N172-O172-P172-Q172-R172-S172-T172)</f>
       </c>
       <c r="W172" s="3">
-        <f>IF($K172="","",(V172-Y172)/J172*100)</f>
+        <f>IF($K172="","",(V172-AC172)/J172*100)</f>
       </c>
       <c r="X172" s="3">
         <f>IF($K172="","",M172-U172)</f>
       </c>
-      <c r="Z172" s="3">
-        <f>IF($K172="","",V172-Y172)</f>
-      </c>
-    </row>
-    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD172" s="3">
+        <f>IF($K172="","",V172-AC172)</f>
+      </c>
+    </row>
+    <row r="173" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="J173" s="3"/>
@@ -8702,16 +8726,16 @@
         <f>IF($K173="","",L173-M173-N173-O173-P173-Q173-R173-S173-T173)</f>
       </c>
       <c r="W173" s="3">
-        <f>IF($K173="","",(V173-Y173)/J173*100)</f>
+        <f>IF($K173="","",(V173-AC173)/J173*100)</f>
       </c>
       <c r="X173" s="3">
         <f>IF($K173="","",M173-U173)</f>
       </c>
-      <c r="Z173" s="3">
-        <f>IF($K173="","",V173-Y173)</f>
-      </c>
-    </row>
-    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD173" s="3">
+        <f>IF($K173="","",V173-AC173)</f>
+      </c>
+    </row>
+    <row r="174" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="J174" s="3"/>
@@ -8748,16 +8772,16 @@
         <f>IF($K174="","",L174-M174-N174-O174-P174-Q174-R174-S174-T174)</f>
       </c>
       <c r="W174" s="3">
-        <f>IF($K174="","",(V174-Y174)/J174*100)</f>
+        <f>IF($K174="","",(V174-AC174)/J174*100)</f>
       </c>
       <c r="X174" s="3">
         <f>IF($K174="","",M174-U174)</f>
       </c>
-      <c r="Z174" s="3">
-        <f>IF($K174="","",V174-Y174)</f>
-      </c>
-    </row>
-    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD174" s="3">
+        <f>IF($K174="","",V174-AC174)</f>
+      </c>
+    </row>
+    <row r="175" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="J175" s="3"/>
@@ -8794,16 +8818,16 @@
         <f>IF($K175="","",L175-M175-N175-O175-P175-Q175-R175-S175-T175)</f>
       </c>
       <c r="W175" s="3">
-        <f>IF($K175="","",(V175-Y175)/J175*100)</f>
+        <f>IF($K175="","",(V175-AC175)/J175*100)</f>
       </c>
       <c r="X175" s="3">
         <f>IF($K175="","",M175-U175)</f>
       </c>
-      <c r="Z175" s="3">
-        <f>IF($K175="","",V175-Y175)</f>
-      </c>
-    </row>
-    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD175" s="3">
+        <f>IF($K175="","",V175-AC175)</f>
+      </c>
+    </row>
+    <row r="176" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="J176" s="3"/>
@@ -8840,16 +8864,16 @@
         <f>IF($K176="","",L176-M176-N176-O176-P176-Q176-R176-S176-T176)</f>
       </c>
       <c r="W176" s="3">
-        <f>IF($K176="","",(V176-Y176)/J176*100)</f>
+        <f>IF($K176="","",(V176-AC176)/J176*100)</f>
       </c>
       <c r="X176" s="3">
         <f>IF($K176="","",M176-U176)</f>
       </c>
-      <c r="Z176" s="3">
-        <f>IF($K176="","",V176-Y176)</f>
-      </c>
-    </row>
-    <row r="177" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD176" s="3">
+        <f>IF($K176="","",V176-AC176)</f>
+      </c>
+    </row>
+    <row r="177" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="J177" s="3"/>
@@ -8886,16 +8910,16 @@
         <f>IF($K177="","",L177-M177-N177-O177-P177-Q177-R177-S177-T177)</f>
       </c>
       <c r="W177" s="3">
-        <f>IF($K177="","",(V177-Y177)/J177*100)</f>
+        <f>IF($K177="","",(V177-AC177)/J177*100)</f>
       </c>
       <c r="X177" s="3">
         <f>IF($K177="","",M177-U177)</f>
       </c>
-      <c r="Z177" s="3">
-        <f>IF($K177="","",V177-Y177)</f>
-      </c>
-    </row>
-    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD177" s="3">
+        <f>IF($K177="","",V177-AC177)</f>
+      </c>
+    </row>
+    <row r="178" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="J178" s="3"/>
@@ -8932,16 +8956,16 @@
         <f>IF($K178="","",L178-M178-N178-O178-P178-Q178-R178-S178-T178)</f>
       </c>
       <c r="W178" s="3">
-        <f>IF($K178="","",(V178-Y178)/J178*100)</f>
+        <f>IF($K178="","",(V178-AC178)/J178*100)</f>
       </c>
       <c r="X178" s="3">
         <f>IF($K178="","",M178-U178)</f>
       </c>
-      <c r="Z178" s="3">
-        <f>IF($K178="","",V178-Y178)</f>
-      </c>
-    </row>
-    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD178" s="3">
+        <f>IF($K178="","",V178-AC178)</f>
+      </c>
+    </row>
+    <row r="179" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="J179" s="3"/>
@@ -8978,16 +9002,16 @@
         <f>IF($K179="","",L179-M179-N179-O179-P179-Q179-R179-S179-T179)</f>
       </c>
       <c r="W179" s="3">
-        <f>IF($K179="","",(V179-Y179)/J179*100)</f>
+        <f>IF($K179="","",(V179-AC179)/J179*100)</f>
       </c>
       <c r="X179" s="3">
         <f>IF($K179="","",M179-U179)</f>
       </c>
-      <c r="Z179" s="3">
-        <f>IF($K179="","",V179-Y179)</f>
-      </c>
-    </row>
-    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD179" s="3">
+        <f>IF($K179="","",V179-AC179)</f>
+      </c>
+    </row>
+    <row r="180" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="J180" s="3"/>
@@ -9024,16 +9048,16 @@
         <f>IF($K180="","",L180-M180-N180-O180-P180-Q180-R180-S180-T180)</f>
       </c>
       <c r="W180" s="3">
-        <f>IF($K180="","",(V180-Y180)/J180*100)</f>
+        <f>IF($K180="","",(V180-AC180)/J180*100)</f>
       </c>
       <c r="X180" s="3">
         <f>IF($K180="","",M180-U180)</f>
       </c>
-      <c r="Z180" s="3">
-        <f>IF($K180="","",V180-Y180)</f>
-      </c>
-    </row>
-    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD180" s="3">
+        <f>IF($K180="","",V180-AC180)</f>
+      </c>
+    </row>
+    <row r="181" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="J181" s="3"/>
@@ -9070,16 +9094,16 @@
         <f>IF($K181="","",L181-M181-N181-O181-P181-Q181-R181-S181-T181)</f>
       </c>
       <c r="W181" s="3">
-        <f>IF($K181="","",(V181-Y181)/J181*100)</f>
+        <f>IF($K181="","",(V181-AC181)/J181*100)</f>
       </c>
       <c r="X181" s="3">
         <f>IF($K181="","",M181-U181)</f>
       </c>
-      <c r="Z181" s="3">
-        <f>IF($K181="","",V181-Y181)</f>
-      </c>
-    </row>
-    <row r="182" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD181" s="3">
+        <f>IF($K181="","",V181-AC181)</f>
+      </c>
+    </row>
+    <row r="182" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="J182" s="3"/>
@@ -9116,16 +9140,16 @@
         <f>IF($K182="","",L182-M182-N182-O182-P182-Q182-R182-S182-T182)</f>
       </c>
       <c r="W182" s="3">
-        <f>IF($K182="","",(V182-Y182)/J182*100)</f>
+        <f>IF($K182="","",(V182-AC182)/J182*100)</f>
       </c>
       <c r="X182" s="3">
         <f>IF($K182="","",M182-U182)</f>
       </c>
-      <c r="Z182" s="3">
-        <f>IF($K182="","",V182-Y182)</f>
-      </c>
-    </row>
-    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD182" s="3">
+        <f>IF($K182="","",V182-AC182)</f>
+      </c>
+    </row>
+    <row r="183" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="J183" s="3"/>
@@ -9162,16 +9186,16 @@
         <f>IF($K183="","",L183-M183-N183-O183-P183-Q183-R183-S183-T183)</f>
       </c>
       <c r="W183" s="3">
-        <f>IF($K183="","",(V183-Y183)/J183*100)</f>
+        <f>IF($K183="","",(V183-AC183)/J183*100)</f>
       </c>
       <c r="X183" s="3">
         <f>IF($K183="","",M183-U183)</f>
       </c>
-      <c r="Z183" s="3">
-        <f>IF($K183="","",V183-Y183)</f>
-      </c>
-    </row>
-    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD183" s="3">
+        <f>IF($K183="","",V183-AC183)</f>
+      </c>
+    </row>
+    <row r="184" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="J184" s="3"/>
@@ -9208,16 +9232,16 @@
         <f>IF($K184="","",L184-M184-N184-O184-P184-Q184-R184-S184-T184)</f>
       </c>
       <c r="W184" s="3">
-        <f>IF($K184="","",(V184-Y184)/J184*100)</f>
+        <f>IF($K184="","",(V184-AC184)/J184*100)</f>
       </c>
       <c r="X184" s="3">
         <f>IF($K184="","",M184-U184)</f>
       </c>
-      <c r="Z184" s="3">
-        <f>IF($K184="","",V184-Y184)</f>
-      </c>
-    </row>
-    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD184" s="3">
+        <f>IF($K184="","",V184-AC184)</f>
+      </c>
+    </row>
+    <row r="185" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="J185" s="3"/>
@@ -9254,16 +9278,16 @@
         <f>IF($K185="","",L185-M185-N185-O185-P185-Q185-R185-S185-T185)</f>
       </c>
       <c r="W185" s="3">
-        <f>IF($K185="","",(V185-Y185)/J185*100)</f>
+        <f>IF($K185="","",(V185-AC185)/J185*100)</f>
       </c>
       <c r="X185" s="3">
         <f>IF($K185="","",M185-U185)</f>
       </c>
-      <c r="Z185" s="3">
-        <f>IF($K185="","",V185-Y185)</f>
-      </c>
-    </row>
-    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD185" s="3">
+        <f>IF($K185="","",V185-AC185)</f>
+      </c>
+    </row>
+    <row r="186" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="J186" s="3"/>
@@ -9300,16 +9324,16 @@
         <f>IF($K186="","",L186-M186-N186-O186-P186-Q186-R186-S186-T186)</f>
       </c>
       <c r="W186" s="3">
-        <f>IF($K186="","",(V186-Y186)/J186*100)</f>
+        <f>IF($K186="","",(V186-AC186)/J186*100)</f>
       </c>
       <c r="X186" s="3">
         <f>IF($K186="","",M186-U186)</f>
       </c>
-      <c r="Z186" s="3">
-        <f>IF($K186="","",V186-Y186)</f>
-      </c>
-    </row>
-    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD186" s="3">
+        <f>IF($K186="","",V186-AC186)</f>
+      </c>
+    </row>
+    <row r="187" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="J187" s="3"/>
@@ -9346,16 +9370,16 @@
         <f>IF($K187="","",L187-M187-N187-O187-P187-Q187-R187-S187-T187)</f>
       </c>
       <c r="W187" s="3">
-        <f>IF($K187="","",(V187-Y187)/J187*100)</f>
+        <f>IF($K187="","",(V187-AC187)/J187*100)</f>
       </c>
       <c r="X187" s="3">
         <f>IF($K187="","",M187-U187)</f>
       </c>
-      <c r="Z187" s="3">
-        <f>IF($K187="","",V187-Y187)</f>
-      </c>
-    </row>
-    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD187" s="3">
+        <f>IF($K187="","",V187-AC187)</f>
+      </c>
+    </row>
+    <row r="188" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="J188" s="3"/>
@@ -9392,16 +9416,16 @@
         <f>IF($K188="","",L188-M188-N188-O188-P188-Q188-R188-S188-T188)</f>
       </c>
       <c r="W188" s="3">
-        <f>IF($K188="","",(V188-Y188)/J188*100)</f>
+        <f>IF($K188="","",(V188-AC188)/J188*100)</f>
       </c>
       <c r="X188" s="3">
         <f>IF($K188="","",M188-U188)</f>
       </c>
-      <c r="Z188" s="3">
-        <f>IF($K188="","",V188-Y188)</f>
-      </c>
-    </row>
-    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD188" s="3">
+        <f>IF($K188="","",V188-AC188)</f>
+      </c>
+    </row>
+    <row r="189" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="J189" s="3"/>
@@ -9438,16 +9462,16 @@
         <f>IF($K189="","",L189-M189-N189-O189-P189-Q189-R189-S189-T189)</f>
       </c>
       <c r="W189" s="3">
-        <f>IF($K189="","",(V189-Y189)/J189*100)</f>
+        <f>IF($K189="","",(V189-AC189)/J189*100)</f>
       </c>
       <c r="X189" s="3">
         <f>IF($K189="","",M189-U189)</f>
       </c>
-      <c r="Z189" s="3">
-        <f>IF($K189="","",V189-Y189)</f>
-      </c>
-    </row>
-    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD189" s="3">
+        <f>IF($K189="","",V189-AC189)</f>
+      </c>
+    </row>
+    <row r="190" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="J190" s="3"/>
@@ -9484,16 +9508,16 @@
         <f>IF($K190="","",L190-M190-N190-O190-P190-Q190-R190-S190-T190)</f>
       </c>
       <c r="W190" s="3">
-        <f>IF($K190="","",(V190-Y190)/J190*100)</f>
+        <f>IF($K190="","",(V190-AC190)/J190*100)</f>
       </c>
       <c r="X190" s="3">
         <f>IF($K190="","",M190-U190)</f>
       </c>
-      <c r="Z190" s="3">
-        <f>IF($K190="","",V190-Y190)</f>
-      </c>
-    </row>
-    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD190" s="3">
+        <f>IF($K190="","",V190-AC190)</f>
+      </c>
+    </row>
+    <row r="191" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="J191" s="3"/>
@@ -9530,16 +9554,16 @@
         <f>IF($K191="","",L191-M191-N191-O191-P191-Q191-R191-S191-T191)</f>
       </c>
       <c r="W191" s="3">
-        <f>IF($K191="","",(V191-Y191)/J191*100)</f>
+        <f>IF($K191="","",(V191-AC191)/J191*100)</f>
       </c>
       <c r="X191" s="3">
         <f>IF($K191="","",M191-U191)</f>
       </c>
-      <c r="Z191" s="3">
-        <f>IF($K191="","",V191-Y191)</f>
-      </c>
-    </row>
-    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD191" s="3">
+        <f>IF($K191="","",V191-AC191)</f>
+      </c>
+    </row>
+    <row r="192" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="J192" s="3"/>
@@ -9576,16 +9600,16 @@
         <f>IF($K192="","",L192-M192-N192-O192-P192-Q192-R192-S192-T192)</f>
       </c>
       <c r="W192" s="3">
-        <f>IF($K192="","",(V192-Y192)/J192*100)</f>
+        <f>IF($K192="","",(V192-AC192)/J192*100)</f>
       </c>
       <c r="X192" s="3">
         <f>IF($K192="","",M192-U192)</f>
       </c>
-      <c r="Z192" s="3">
-        <f>IF($K192="","",V192-Y192)</f>
-      </c>
-    </row>
-    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD192" s="3">
+        <f>IF($K192="","",V192-AC192)</f>
+      </c>
+    </row>
+    <row r="193" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="J193" s="3"/>
@@ -9622,16 +9646,16 @@
         <f>IF($K193="","",L193-M193-N193-O193-P193-Q193-R193-S193-T193)</f>
       </c>
       <c r="W193" s="3">
-        <f>IF($K193="","",(V193-Y193)/J193*100)</f>
+        <f>IF($K193="","",(V193-AC193)/J193*100)</f>
       </c>
       <c r="X193" s="3">
         <f>IF($K193="","",M193-U193)</f>
       </c>
-      <c r="Z193" s="3">
-        <f>IF($K193="","",V193-Y193)</f>
-      </c>
-    </row>
-    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD193" s="3">
+        <f>IF($K193="","",V193-AC193)</f>
+      </c>
+    </row>
+    <row r="194" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="J194" s="3"/>
@@ -9668,16 +9692,16 @@
         <f>IF($K194="","",L194-M194-N194-O194-P194-Q194-R194-S194-T194)</f>
       </c>
       <c r="W194" s="3">
-        <f>IF($K194="","",(V194-Y194)/J194*100)</f>
+        <f>IF($K194="","",(V194-AC194)/J194*100)</f>
       </c>
       <c r="X194" s="3">
         <f>IF($K194="","",M194-U194)</f>
       </c>
-      <c r="Z194" s="3">
-        <f>IF($K194="","",V194-Y194)</f>
-      </c>
-    </row>
-    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD194" s="3">
+        <f>IF($K194="","",V194-AC194)</f>
+      </c>
+    </row>
+    <row r="195" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="J195" s="3"/>
@@ -9714,16 +9738,16 @@
         <f>IF($K195="","",L195-M195-N195-O195-P195-Q195-R195-S195-T195)</f>
       </c>
       <c r="W195" s="3">
-        <f>IF($K195="","",(V195-Y195)/J195*100)</f>
+        <f>IF($K195="","",(V195-AC195)/J195*100)</f>
       </c>
       <c r="X195" s="3">
         <f>IF($K195="","",M195-U195)</f>
       </c>
-      <c r="Z195" s="3">
-        <f>IF($K195="","",V195-Y195)</f>
-      </c>
-    </row>
-    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD195" s="3">
+        <f>IF($K195="","",V195-AC195)</f>
+      </c>
+    </row>
+    <row r="196" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="J196" s="3"/>
@@ -9760,16 +9784,16 @@
         <f>IF($K196="","",L196-M196-N196-O196-P196-Q196-R196-S196-T196)</f>
       </c>
       <c r="W196" s="3">
-        <f>IF($K196="","",(V196-Y196)/J196*100)</f>
+        <f>IF($K196="","",(V196-AC196)/J196*100)</f>
       </c>
       <c r="X196" s="3">
         <f>IF($K196="","",M196-U196)</f>
       </c>
-      <c r="Z196" s="3">
-        <f>IF($K196="","",V196-Y196)</f>
-      </c>
-    </row>
-    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD196" s="3">
+        <f>IF($K196="","",V196-AC196)</f>
+      </c>
+    </row>
+    <row r="197" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="J197" s="3"/>
@@ -9806,16 +9830,16 @@
         <f>IF($K197="","",L197-M197-N197-O197-P197-Q197-R197-S197-T197)</f>
       </c>
       <c r="W197" s="3">
-        <f>IF($K197="","",(V197-Y197)/J197*100)</f>
+        <f>IF($K197="","",(V197-AC197)/J197*100)</f>
       </c>
       <c r="X197" s="3">
         <f>IF($K197="","",M197-U197)</f>
       </c>
-      <c r="Z197" s="3">
-        <f>IF($K197="","",V197-Y197)</f>
-      </c>
-    </row>
-    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD197" s="3">
+        <f>IF($K197="","",V197-AC197)</f>
+      </c>
+    </row>
+    <row r="198" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="J198" s="3"/>
@@ -9852,16 +9876,16 @@
         <f>IF($K198="","",L198-M198-N198-O198-P198-Q198-R198-S198-T198)</f>
       </c>
       <c r="W198" s="3">
-        <f>IF($K198="","",(V198-Y198)/J198*100)</f>
+        <f>IF($K198="","",(V198-AC198)/J198*100)</f>
       </c>
       <c r="X198" s="3">
         <f>IF($K198="","",M198-U198)</f>
       </c>
-      <c r="Z198" s="3">
-        <f>IF($K198="","",V198-Y198)</f>
-      </c>
-    </row>
-    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD198" s="3">
+        <f>IF($K198="","",V198-AC198)</f>
+      </c>
+    </row>
+    <row r="199" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="J199" s="3"/>
@@ -9898,16 +9922,16 @@
         <f>IF($K199="","",L199-M199-N199-O199-P199-Q199-R199-S199-T199)</f>
       </c>
       <c r="W199" s="3">
-        <f>IF($K199="","",(V199-Y199)/J199*100)</f>
+        <f>IF($K199="","",(V199-AC199)/J199*100)</f>
       </c>
       <c r="X199" s="3">
         <f>IF($K199="","",M199-U199)</f>
       </c>
-      <c r="Z199" s="3">
-        <f>IF($K199="","",V199-Y199)</f>
-      </c>
-    </row>
-    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD199" s="3">
+        <f>IF($K199="","",V199-AC199)</f>
+      </c>
+    </row>
+    <row r="200" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="J200" s="3"/>
@@ -9944,16 +9968,16 @@
         <f>IF($K200="","",L200-M200-N200-O200-P200-Q200-R200-S200-T200)</f>
       </c>
       <c r="W200" s="3">
-        <f>IF($K200="","",(V200-Y200)/J200*100)</f>
+        <f>IF($K200="","",(V200-AC200)/J200*100)</f>
       </c>
       <c r="X200" s="3">
         <f>IF($K200="","",M200-U200)</f>
       </c>
-      <c r="Z200" s="3">
-        <f>IF($K200="","",V200-Y200)</f>
-      </c>
-    </row>
-    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD200" s="3">
+        <f>IF($K200="","",V200-AC200)</f>
+      </c>
+    </row>
+    <row r="201" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="J201" s="3"/>
@@ -9990,16 +10014,16 @@
         <f>IF($K201="","",L201-M201-N201-O201-P201-Q201-R201-S201-T201)</f>
       </c>
       <c r="W201" s="3">
-        <f>IF($K201="","",(V201-Y201)/J201*100)</f>
+        <f>IF($K201="","",(V201-AC201)/J201*100)</f>
       </c>
       <c r="X201" s="3">
         <f>IF($K201="","",M201-U201)</f>
       </c>
-      <c r="Z201" s="3">
-        <f>IF($K201="","",V201-Y201)</f>
-      </c>
-    </row>
-    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AD201" s="3">
+        <f>IF($K201="","",V201-AC201)</f>
+      </c>
+    </row>
+    <row r="202" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="J202" s="3"/>
@@ -10036,18 +10060,18 @@
         <f>IF($K202="","",L202-M202-N202-O202-P202-Q202-R202-S202-T202)</f>
       </c>
       <c r="W202" s="3">
-        <f>IF($K202="","",(V202-Y202)/J202*100)</f>
+        <f>IF($K202="","",(V202-AC202)/J202*100)</f>
       </c>
       <c r="X202" s="3">
         <f>IF($K202="","",M202-U202)</f>
       </c>
-      <c r="Z202" s="3">
-        <f>IF($K202="","",V202-Y202)</f>
-      </c>
-    </row>
-    <row r="203" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD202" s="3">
+        <f>IF($K202="","",V202-AC202)</f>
+      </c>
+    </row>
+    <row r="203" spans="1:35" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -10099,7 +10123,7 @@
         <f>SUM(V2:V202)</f>
       </c>
       <c r="W203" s="6">
-        <f>IFERROR((V203-Y203)/J203*100,0)</f>
+        <f>IFERROR((V203-AC203)/J203*100,0)</f>
       </c>
       <c r="X203" s="6">
         <f>SUM(X2:X202)</f>
@@ -10110,11 +10134,23 @@
       <c r="Z203" s="6">
         <f>SUM(Z2:Z202)</f>
       </c>
-      <c r="AA203" s="4"/>
-      <c r="AB203" s="4"/>
-      <c r="AC203" s="4"/>
-      <c r="AD203" s="4"/>
+      <c r="AA203" s="6">
+        <f>SUM(AA2:AA202)</f>
+      </c>
+      <c r="AB203" s="6">
+        <f>SUM(AB2:AB202)</f>
+      </c>
+      <c r="AC203" s="6">
+        <f>SUM(AC2:AC202)</f>
+      </c>
+      <c r="AD203" s="6">
+        <f>SUM(AD2:AD202)</f>
+      </c>
       <c r="AE203" s="4"/>
+      <c r="AF203" s="4"/>
+      <c r="AG203" s="4"/>
+      <c r="AH203" s="4"/>
+      <c r="AI203" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
